--- a/testHub/testCases.xlsx
+++ b/testHub/testCases.xlsx
@@ -463,296 +463,296 @@
   </cols>
   <sheetData>
     <row r="1">
-      <c r="A1" s="1" t="inlineStr">
+      <c r="A1" t="inlineStr">
         <is>
           <t>模块</t>
         </is>
       </c>
-      <c r="B1" s="1" t="inlineStr">
+      <c r="B1" t="inlineStr">
         <is>
           <t>类名</t>
         </is>
       </c>
-      <c r="C1" s="1" t="inlineStr">
+      <c r="C1" t="inlineStr">
         <is>
           <t>构造型</t>
         </is>
       </c>
-      <c r="D1" s="1" t="inlineStr">
+      <c r="D1" t="inlineStr">
         <is>
           <t>用例数</t>
         </is>
       </c>
-      <c r="E1" s="1" t="inlineStr">
+      <c r="E1" t="inlineStr">
         <is>
           <t>优先级分布</t>
         </is>
       </c>
-      <c r="F1" s="1" t="inlineStr">
+      <c r="F1" t="inlineStr">
         <is>
           <t>关系</t>
         </is>
       </c>
-      <c r="G1" s="1" t="inlineStr">
+      <c r="G1" t="inlineStr">
         <is>
           <t>备注</t>
         </is>
       </c>
     </row>
     <row r="2">
-      <c r="A2" s="2" t="inlineStr">
+      <c r="A2" t="inlineStr">
         <is>
           <t>任务基类</t>
         </is>
       </c>
-      <c r="B2" s="2" t="inlineStr">
+      <c r="B2" t="inlineStr">
         <is>
           <t>BaseTask</t>
         </is>
       </c>
-      <c r="C2" s="2" t="inlineStr">
+      <c r="C2" t="inlineStr">
         <is>
           <t>abstract</t>
         </is>
       </c>
-      <c r="D2" s="2" t="inlineStr">
+      <c r="D2" t="inlineStr">
         <is>
           <t>7</t>
         </is>
       </c>
-      <c r="E2" s="2" t="inlineStr">
+      <c r="E2" t="inlineStr">
         <is>
           <t>P0:3, P1:2, P2:2</t>
         </is>
       </c>
-      <c r="F2" s="2" t="inlineStr">
+      <c r="F2" t="inlineStr">
         <is>
           <t>OtaTask/CrowTask/SentinelTask继承</t>
         </is>
       </c>
-      <c r="G2" s="2" t="inlineStr">
+      <c r="G2" t="inlineStr">
         <is>
           <t>抽象基类，execute()为抽象方法</t>
         </is>
       </c>
     </row>
     <row r="3">
-      <c r="A3" s="2" t="inlineStr">
+      <c r="A3" t="inlineStr">
         <is>
           <t>升级任务</t>
         </is>
       </c>
-      <c r="B3" s="2" t="inlineStr">
+      <c r="B3" t="inlineStr">
         <is>
           <t>OtaTask</t>
         </is>
       </c>
-      <c r="C3" s="2" t="inlineStr">
+      <c r="C3" t="inlineStr">
         <is>
           <t>class</t>
         </is>
       </c>
-      <c r="D3" s="2" t="inlineStr">
+      <c r="D3" t="inlineStr">
         <is>
           <t>8</t>
         </is>
       </c>
-      <c r="E3" s="2" t="inlineStr">
+      <c r="E3" t="inlineStr">
         <is>
           <t>P0:4, P1:3, P2:1</t>
         </is>
       </c>
-      <c r="F3" s="2" t="inlineStr">
+      <c r="F3" t="inlineStr">
         <is>
           <t>继承BaseTask, 关联TaskScheduler</t>
         </is>
       </c>
-      <c r="G3" s="2" t="inlineStr">
+      <c r="G3" t="inlineStr">
         <is>
           <t>随机升级，清除鸡叫累计和预约</t>
         </is>
       </c>
     </row>
     <row r="4">
-      <c r="A4" s="2" t="inlineStr">
+      <c r="A4" t="inlineStr">
         <is>
           <t>鸡叫任务</t>
         </is>
       </c>
-      <c r="B4" s="2" t="inlineStr">
+      <c r="B4" t="inlineStr">
         <is>
           <t>CrowTask</t>
         </is>
       </c>
-      <c r="C4" s="2" t="inlineStr">
+      <c r="C4" t="inlineStr">
         <is>
           <t>class</t>
         </is>
       </c>
-      <c r="D4" s="2" t="inlineStr">
+      <c r="D4" t="inlineStr">
         <is>
           <t>10</t>
         </is>
       </c>
-      <c r="E4" s="2" t="inlineStr">
+      <c r="E4" t="inlineStr">
         <is>
           <t>P0:5, P1:3, P2:2</t>
         </is>
       </c>
-      <c r="F4" s="2" t="inlineStr">
+      <c r="F4" t="inlineStr">
         <is>
           <t>继承BaseTask, 聚合到TaskScheduler</t>
         </is>
       </c>
-      <c r="G4" s="2" t="inlineStr">
+      <c r="G4" t="inlineStr">
         <is>
           <t>每7天鸡叫，2:00-4:00随机，不可打断</t>
         </is>
       </c>
     </row>
     <row r="5">
-      <c r="A5" s="2" t="inlineStr">
+      <c r="A5" t="inlineStr">
         <is>
           <t>哨兵任务</t>
         </is>
       </c>
-      <c r="B5" s="2" t="inlineStr">
+      <c r="B5" t="inlineStr">
         <is>
           <t>SentinelTask</t>
         </is>
       </c>
-      <c r="C5" s="2" t="inlineStr">
+      <c r="C5" t="inlineStr">
         <is>
           <t>class</t>
         </is>
       </c>
-      <c r="D5" s="2" t="inlineStr">
+      <c r="D5" t="inlineStr">
         <is>
           <t>9</t>
         </is>
       </c>
-      <c r="E5" s="2" t="inlineStr">
+      <c r="E5" t="inlineStr">
         <is>
           <t>P0:4, P1:3, P2:2</t>
         </is>
       </c>
-      <c r="F5" s="2" t="inlineStr">
+      <c r="F5" t="inlineStr">
         <is>
           <t>继承BaseTask, 关联TaskScheduler</t>
         </is>
       </c>
-      <c r="G5" s="2" t="inlineStr">
+      <c r="G5" t="inlineStr">
         <is>
           <t>可被CrowTask/OtaTask打断并恢复</t>
         </is>
       </c>
     </row>
     <row r="6">
-      <c r="A6" s="2" t="inlineStr">
+      <c r="A6" t="inlineStr">
         <is>
           <t>任务调度器</t>
         </is>
       </c>
-      <c r="B6" s="2" t="inlineStr">
+      <c r="B6" t="inlineStr">
         <is>
           <t>TaskScheduler</t>
         </is>
       </c>
-      <c r="C6" s="2" t="inlineStr">
+      <c r="C6" t="inlineStr">
         <is>
           <t>class</t>
         </is>
       </c>
-      <c r="D6" s="2" t="inlineStr">
+      <c r="D6" t="inlineStr">
         <is>
           <t>11</t>
         </is>
       </c>
-      <c r="E6" s="2" t="inlineStr">
+      <c r="E6" t="inlineStr">
         <is>
           <t>P0:5, P1:4, P2:2</t>
         </is>
       </c>
-      <c r="F6" s="2" t="inlineStr">
+      <c r="F6" t="inlineStr">
         <is>
           <t>聚合到MM_APP, 聚合CrowTask</t>
         </is>
       </c>
-      <c r="G6" s="2" t="inlineStr">
+      <c r="G6" t="inlineStr">
         <is>
           <t>任务增删调度，按优先级执行</t>
         </is>
       </c>
     </row>
     <row r="7">
-      <c r="A7" s="2" t="inlineStr">
+      <c r="A7" t="inlineStr">
         <is>
           <t>主应用</t>
         </is>
       </c>
-      <c r="B7" s="2" t="inlineStr">
+      <c r="B7" t="inlineStr">
         <is>
           <t>MM_APP</t>
         </is>
       </c>
-      <c r="C7" s="2" t="inlineStr">
+      <c r="C7" t="inlineStr">
         <is>
           <t>class</t>
         </is>
       </c>
-      <c r="D7" s="2" t="inlineStr">
+      <c r="D7" t="inlineStr">
         <is>
           <t>6</t>
         </is>
       </c>
-      <c r="E7" s="2" t="inlineStr">
+      <c r="E7" t="inlineStr">
         <is>
           <t>P0:3, P1:2, P2:1</t>
         </is>
       </c>
-      <c r="F7" s="2" t="inlineStr">
+      <c r="F7" t="inlineStr">
         <is>
           <t>聚合TaskScheduler</t>
         </is>
       </c>
-      <c r="G7" s="2" t="inlineStr">
+      <c r="G7" t="inlineStr">
         <is>
           <t>应用启停入口</t>
         </is>
       </c>
     </row>
     <row r="8">
-      <c r="A8" s="2" t="inlineStr">
+      <c r="A8" t="inlineStr">
         <is>
           <t>集成测试</t>
         </is>
       </c>
-      <c r="B8" s="2" t="inlineStr">
+      <c r="B8" t="inlineStr">
         <is>
           <t>-</t>
         </is>
       </c>
-      <c r="C8" s="2" t="inlineStr">
+      <c r="C8" t="inlineStr">
         <is>
           <t>-</t>
         </is>
       </c>
-      <c r="D8" s="2" t="inlineStr">
+      <c r="D8" t="inlineStr">
         <is>
           <t>12</t>
         </is>
       </c>
-      <c r="E8" s="2" t="inlineStr">
+      <c r="E8" t="inlineStr">
         <is>
           <t>P0:6, P1:4, P2:2</t>
         </is>
       </c>
-      <c r="F8" s="2" t="inlineStr">
+      <c r="F8" t="inlineStr">
         <is>
           <t>全链路</t>
         </is>
       </c>
-      <c r="G8" s="2" t="inlineStr">
+      <c r="G8" t="inlineStr">
         <is>
           <t>跨模块集成场景</t>
         </is>
@@ -779,63 +779,63 @@
   </cols>
   <sheetData>
     <row r="1">
-      <c r="A1" s="1" t="inlineStr">
+      <c r="A1" t="inlineStr">
         <is>
           <t>类名</t>
         </is>
       </c>
-      <c r="B1" s="1" t="inlineStr">
+      <c r="B1" t="inlineStr">
         <is>
           <t>构造型</t>
         </is>
       </c>
-      <c r="C1" s="1" t="inlineStr">
+      <c r="C1" t="inlineStr">
         <is>
           <t>关键属性</t>
         </is>
       </c>
-      <c r="D1" s="1" t="inlineStr">
+      <c r="D1" t="inlineStr">
         <is>
           <t>关键方法</t>
         </is>
       </c>
     </row>
     <row r="2">
-      <c r="A2" s="2" t="inlineStr">
+      <c r="A2" t="inlineStr">
         <is>
           <t>OtaTask</t>
         </is>
       </c>
-      <c r="B2" s="2" t="inlineStr">
+      <c r="B2" t="inlineStr">
         <is>
           <t>class</t>
         </is>
       </c>
-      <c r="C2" s="2" t="inlineStr">
+      <c r="C2" t="inlineStr">
         <is>
           <t>+ isRandom: association
 + clearCrowAccumulation: association
 + clearScheduledCrow: association</t>
         </is>
       </c>
-      <c r="D2" s="2" t="inlineStr">
+      <c r="D2" t="inlineStr">
         <is>
           <t xml:space="preserve">+ execute(): </t>
         </is>
       </c>
     </row>
     <row r="3">
-      <c r="A3" s="2" t="inlineStr">
+      <c r="A3" t="inlineStr">
         <is>
           <t>CrowTask</t>
         </is>
       </c>
-      <c r="B3" s="2" t="inlineStr">
+      <c r="B3" t="inlineStr">
         <is>
           <t>class</t>
         </is>
       </c>
-      <c r="C3" s="2" t="inlineStr">
+      <c r="C3" t="inlineStr">
         <is>
           <t>+ intervalDays: association
 # scheduledTime: association
@@ -843,7 +843,7 @@
 + crowFlag: association</t>
         </is>
       </c>
-      <c r="D3" s="2" t="inlineStr">
+      <c r="D3" t="inlineStr">
         <is>
           <t xml:space="preserve">+ scheduleNextCrow(): 
 + clearCrowFlag(): </t>
@@ -851,22 +851,22 @@
       </c>
     </row>
     <row r="4">
-      <c r="A4" s="2" t="inlineStr">
+      <c r="A4" t="inlineStr">
         <is>
           <t>TaskScheduler</t>
         </is>
       </c>
-      <c r="B4" s="2" t="inlineStr">
+      <c r="B4" t="inlineStr">
         <is>
           <t>class</t>
         </is>
       </c>
-      <c r="C4" s="2" t="inlineStr">
+      <c r="C4" t="inlineStr">
         <is>
           <t>- taskList: association</t>
         </is>
       </c>
-      <c r="D4" s="2" t="inlineStr">
+      <c r="D4" t="inlineStr">
         <is>
           <t xml:space="preserve">+ addTask(): 
 + removeTask(): 
@@ -875,23 +875,23 @@
       </c>
     </row>
     <row r="5">
-      <c r="A5" s="2" t="inlineStr">
+      <c r="A5" t="inlineStr">
         <is>
           <t>MM_APP</t>
         </is>
       </c>
-      <c r="B5" s="2" t="inlineStr">
+      <c r="B5" t="inlineStr">
         <is>
           <t>class</t>
         </is>
       </c>
-      <c r="C5" s="2" t="inlineStr">
+      <c r="C5" t="inlineStr">
         <is>
           <t>+ appName: association
 + version: association</t>
         </is>
       </c>
-      <c r="D5" s="2" t="inlineStr">
+      <c r="D5" t="inlineStr">
         <is>
           <t xml:space="preserve">+ start(): 
 + stop(): </t>
@@ -899,23 +899,23 @@
       </c>
     </row>
     <row r="6">
-      <c r="A6" s="2" t="inlineStr">
+      <c r="A6" t="inlineStr">
         <is>
           <t>SentinelTask</t>
         </is>
       </c>
-      <c r="B6" s="2" t="inlineStr">
+      <c r="B6" t="inlineStr">
         <is>
           <t>class</t>
         </is>
       </c>
-      <c r="C6" s="2" t="inlineStr">
+      <c r="C6" t="inlineStr">
         <is>
           <t>- isRunning: association
 - interruptedBy: association</t>
         </is>
       </c>
-      <c r="D6" s="2" t="inlineStr">
+      <c r="D6" t="inlineStr">
         <is>
           <t>+ execute(): void
 + interrupt(): void
@@ -924,23 +924,23 @@
       </c>
     </row>
     <row r="7">
-      <c r="A7" s="2" t="inlineStr">
+      <c r="A7" t="inlineStr">
         <is>
           <t>BaseTask</t>
         </is>
       </c>
-      <c r="B7" s="2" t="inlineStr">
+      <c r="B7" t="inlineStr">
         <is>
           <t>abstract</t>
         </is>
       </c>
-      <c r="C7" s="2" t="inlineStr">
+      <c r="C7" t="inlineStr">
         <is>
           <t>- taskId: association
 # priority: association</t>
         </is>
       </c>
-      <c r="D7" s="2" t="inlineStr">
+      <c r="D7" t="inlineStr">
         <is>
           <t>+ execute(): void
 + getTaskId(): String</t>
@@ -972,288 +972,288 @@
   </cols>
   <sheetData>
     <row r="1">
-      <c r="A1" s="1" t="inlineStr">
+      <c r="A1" t="inlineStr">
         <is>
           <t>用例ID</t>
         </is>
       </c>
-      <c r="B1" s="1" t="inlineStr">
+      <c r="B1" t="inlineStr">
         <is>
           <t>用例名称</t>
         </is>
       </c>
-      <c r="C1" s="1" t="inlineStr">
+      <c r="C1" t="inlineStr">
         <is>
           <t>优先级</t>
         </is>
       </c>
-      <c r="D1" s="1" t="inlineStr">
+      <c r="D1" t="inlineStr">
         <is>
           <t>前置条件</t>
         </is>
       </c>
-      <c r="E1" s="1" t="inlineStr">
+      <c r="E1" t="inlineStr">
         <is>
           <t>测试步骤</t>
         </is>
       </c>
-      <c r="F1" s="1" t="inlineStr">
+      <c r="F1" t="inlineStr">
         <is>
           <t>预期结果</t>
         </is>
       </c>
-      <c r="G1" s="1" t="inlineStr">
+      <c r="G1" t="inlineStr">
         <is>
           <t>测试类型</t>
         </is>
       </c>
-      <c r="H1" s="1" t="inlineStr">
+      <c r="H1" t="inlineStr">
         <is>
           <t>状态</t>
         </is>
       </c>
     </row>
     <row r="2">
-      <c r="A2" s="2" t="inlineStr">
+      <c r="A2" t="inlineStr">
         <is>
           <t>TC-BASE-001</t>
         </is>
       </c>
-      <c r="B2" s="2" t="inlineStr">
+      <c r="B2" t="inlineStr">
         <is>
           <t>创建BaseTask子类实例</t>
         </is>
       </c>
-      <c r="C2" s="2" t="inlineStr">
+      <c r="C2" t="inlineStr">
         <is>
           <t>P0</t>
         </is>
       </c>
-      <c r="D2" s="2" t="inlineStr">
+      <c r="D2" t="inlineStr">
         <is>
           <t>无</t>
         </is>
       </c>
-      <c r="E2" s="2" t="inlineStr">
+      <c r="E2" t="inlineStr">
         <is>
           <t>1.创建OtaTask实例
 2.检查taskId不为空
 3.检查priority默认值为0</t>
         </is>
       </c>
-      <c r="F2" s="2" t="inlineStr">
+      <c r="F2" t="inlineStr">
         <is>
           <t>实例创建成功，taskId自动生成，priority=0</t>
         </is>
       </c>
-      <c r="G2" s="2" t="inlineStr">
+      <c r="G2" t="inlineStr">
         <is>
           <t>单元测试</t>
         </is>
       </c>
-      <c r="H2" s="2" t="inlineStr">
+      <c r="H2" t="inlineStr">
         <is>
           <t>待执行</t>
         </is>
       </c>
     </row>
     <row r="3">
-      <c r="A3" s="2" t="inlineStr">
+      <c r="A3" t="inlineStr">
         <is>
           <t>TC-BASE-002</t>
         </is>
       </c>
-      <c r="B3" s="2" t="inlineStr">
+      <c r="B3" t="inlineStr">
         <is>
           <t>getTaskId返回正确ID</t>
         </is>
       </c>
-      <c r="C3" s="2" t="inlineStr">
+      <c r="C3" t="inlineStr">
         <is>
           <t>P0</t>
         </is>
       </c>
-      <c r="D3" s="2" t="inlineStr">
+      <c r="D3" t="inlineStr">
         <is>
           <t>BaseTask子类已创建</t>
         </is>
       </c>
-      <c r="E3" s="2" t="inlineStr">
+      <c r="E3" t="inlineStr">
         <is>
           <t>1.创建CrowTask实例
 2.调用getTaskId()
 3.验证返回值</t>
         </is>
       </c>
-      <c r="F3" s="2" t="inlineStr">
+      <c r="F3" t="inlineStr">
         <is>
           <t>返回的taskId与创建时一致</t>
         </is>
       </c>
-      <c r="G3" s="2" t="inlineStr">
+      <c r="G3" t="inlineStr">
         <is>
           <t>单元测试</t>
         </is>
       </c>
-      <c r="H3" s="2" t="inlineStr">
+      <c r="H3" t="inlineStr">
         <is>
           <t>待执行</t>
         </is>
       </c>
     </row>
     <row r="4">
-      <c r="A4" s="2" t="inlineStr">
+      <c r="A4" t="inlineStr">
         <is>
           <t>TC-BASE-003</t>
         </is>
       </c>
-      <c r="B4" s="2" t="inlineStr">
+      <c r="B4" t="inlineStr">
         <is>
           <t>子类重写execute方法</t>
         </is>
       </c>
-      <c r="C4" s="2" t="inlineStr">
+      <c r="C4" t="inlineStr">
         <is>
           <t>P0</t>
         </is>
       </c>
-      <c r="D4" s="2" t="inlineStr">
+      <c r="D4" t="inlineStr">
         <is>
           <t>各子类已创建</t>
         </is>
       </c>
-      <c r="E4" s="2" t="inlineStr">
+      <c r="E4" t="inlineStr">
         <is>
           <t>1.调用OtaTask.execute()
 2.调用CrowTask.execute()
 3.调用SentinelTask.execute()</t>
         </is>
       </c>
-      <c r="F4" s="2" t="inlineStr">
+      <c r="F4" t="inlineStr">
         <is>
           <t>各子类执行各自execute逻辑，不抛异常</t>
         </is>
       </c>
-      <c r="G4" s="2" t="inlineStr">
+      <c r="G4" t="inlineStr">
         <is>
           <t>单元测试</t>
         </is>
       </c>
-      <c r="H4" s="2" t="inlineStr">
+      <c r="H4" t="inlineStr">
         <is>
           <t>待执行</t>
         </is>
       </c>
     </row>
     <row r="5">
-      <c r="A5" s="2" t="inlineStr">
+      <c r="A5" t="inlineStr">
         <is>
           <t>TC-BASE-004</t>
         </is>
       </c>
-      <c r="B5" s="2" t="inlineStr">
+      <c r="B5" t="inlineStr">
         <is>
           <t>BaseTask不可直接实例化</t>
         </is>
       </c>
-      <c r="C5" s="2" t="inlineStr">
+      <c r="C5" t="inlineStr">
         <is>
           <t>P1</t>
         </is>
       </c>
-      <c r="D5" s="2" t="inlineStr">
+      <c r="D5" t="inlineStr">
         <is>
           <t>无</t>
         </is>
       </c>
-      <c r="E5" s="2" t="inlineStr">
+      <c r="E5" t="inlineStr">
         <is>
           <t>1.尝试直接创建BaseTask实例
 2.调用execute()</t>
         </is>
       </c>
-      <c r="F5" s="2" t="inlineStr">
+      <c r="F5" t="inlineStr">
         <is>
           <t>创建失败或execute()抛NotImplementedError</t>
         </is>
       </c>
-      <c r="G5" s="2" t="inlineStr">
+      <c r="G5" t="inlineStr">
         <is>
           <t>单元测试</t>
         </is>
       </c>
-      <c r="H5" s="2" t="inlineStr">
+      <c r="H5" t="inlineStr">
         <is>
           <t>待执行</t>
         </is>
       </c>
     </row>
     <row r="6">
-      <c r="A6" s="2" t="inlineStr">
+      <c r="A6" t="inlineStr">
         <is>
           <t>TC-BASE-005</t>
         </is>
       </c>
-      <c r="B6" s="2" t="inlineStr">
+      <c r="B6" t="inlineStr">
         <is>
           <t>priority边界值测试</t>
         </is>
       </c>
-      <c r="C6" s="2" t="inlineStr">
+      <c r="C6" t="inlineStr">
         <is>
           <t>P1</t>
         </is>
       </c>
-      <c r="D6" s="2" t="inlineStr">
+      <c r="D6" t="inlineStr">
         <is>
           <t>子类已创建</t>
         </is>
       </c>
-      <c r="E6" s="2" t="inlineStr">
+      <c r="E6" t="inlineStr">
         <is>
           <t>1.设置priority=Integer.MAX
 2.设置priority=Integer.MIN
 3.设置priority=-1</t>
         </is>
       </c>
-      <c r="F6" s="2" t="inlineStr">
+      <c r="F6" t="inlineStr">
         <is>
           <t>边界值正常存储，不报错</t>
         </is>
       </c>
-      <c r="G6" s="2" t="inlineStr">
+      <c r="G6" t="inlineStr">
         <is>
           <t>单元测试</t>
         </is>
       </c>
-      <c r="H6" s="2" t="inlineStr">
+      <c r="H6" t="inlineStr">
         <is>
           <t>待执行</t>
         </is>
       </c>
     </row>
     <row r="7">
-      <c r="A7" s="2" t="inlineStr">
+      <c r="A7" t="inlineStr">
         <is>
           <t>TC-BASE-006</t>
         </is>
       </c>
-      <c r="B7" s="2" t="inlineStr">
+      <c r="B7" t="inlineStr">
         <is>
           <t>多子类taskId唯一性</t>
         </is>
       </c>
-      <c r="C7" s="2" t="inlineStr">
+      <c r="C7" t="inlineStr">
         <is>
           <t>P2</t>
         </is>
       </c>
-      <c r="D7" s="2" t="inlineStr">
+      <c r="D7" t="inlineStr">
         <is>
           <t>无</t>
         </is>
       </c>
-      <c r="E7" s="2" t="inlineStr">
+      <c r="E7" t="inlineStr">
         <is>
           <t>1.创建OtaTask
 2.创建CrowTask
@@ -1261,60 +1261,60 @@
 4.比较三者taskId</t>
         </is>
       </c>
-      <c r="F7" s="2" t="inlineStr">
+      <c r="F7" t="inlineStr">
         <is>
           <t>三个taskId互不相同</t>
         </is>
       </c>
-      <c r="G7" s="2" t="inlineStr">
+      <c r="G7" t="inlineStr">
         <is>
           <t>单元测试</t>
         </is>
       </c>
-      <c r="H7" s="2" t="inlineStr">
+      <c r="H7" t="inlineStr">
         <is>
           <t>待执行</t>
         </is>
       </c>
     </row>
     <row r="8">
-      <c r="A8" s="2" t="inlineStr">
+      <c r="A8" t="inlineStr">
         <is>
           <t>TC-BASE-007</t>
         </is>
       </c>
-      <c r="B8" s="2" t="inlineStr">
+      <c r="B8" t="inlineStr">
         <is>
           <t>protected属性子类访问</t>
         </is>
       </c>
-      <c r="C8" s="2" t="inlineStr">
+      <c r="C8" t="inlineStr">
         <is>
           <t>P2</t>
         </is>
       </c>
-      <c r="D8" s="2" t="inlineStr">
+      <c r="D8" t="inlineStr">
         <is>
           <t>子类已创建</t>
         </is>
       </c>
-      <c r="E8" s="2" t="inlineStr">
+      <c r="E8" t="inlineStr">
         <is>
           <t>1.在CrowTask中访问priority
 2.修改priority值</t>
         </is>
       </c>
-      <c r="F8" s="2" t="inlineStr">
+      <c r="F8" t="inlineStr">
         <is>
           <t>子类可读写protected属性</t>
         </is>
       </c>
-      <c r="G8" s="2" t="inlineStr">
+      <c r="G8" t="inlineStr">
         <is>
           <t>单元测试</t>
         </is>
       </c>
-      <c r="H8" s="2" t="inlineStr">
+      <c r="H8" t="inlineStr">
         <is>
           <t>待执行</t>
         </is>
@@ -1345,390 +1345,390 @@
   </cols>
   <sheetData>
     <row r="1">
-      <c r="A1" s="1" t="inlineStr">
+      <c r="A1" t="inlineStr">
         <is>
           <t>用例ID</t>
         </is>
       </c>
-      <c r="B1" s="1" t="inlineStr">
+      <c r="B1" t="inlineStr">
         <is>
           <t>用例名称</t>
         </is>
       </c>
-      <c r="C1" s="1" t="inlineStr">
+      <c r="C1" t="inlineStr">
         <is>
           <t>优先级</t>
         </is>
       </c>
-      <c r="D1" s="1" t="inlineStr">
+      <c r="D1" t="inlineStr">
         <is>
           <t>前置条件</t>
         </is>
       </c>
-      <c r="E1" s="1" t="inlineStr">
+      <c r="E1" t="inlineStr">
         <is>
           <t>测试步骤</t>
         </is>
       </c>
-      <c r="F1" s="1" t="inlineStr">
+      <c r="F1" t="inlineStr">
         <is>
           <t>预期结果</t>
         </is>
       </c>
-      <c r="G1" s="1" t="inlineStr">
+      <c r="G1" t="inlineStr">
         <is>
           <t>测试类型</t>
         </is>
       </c>
-      <c r="H1" s="1" t="inlineStr">
+      <c r="H1" t="inlineStr">
         <is>
           <t>状态</t>
         </is>
       </c>
     </row>
     <row r="2">
-      <c r="A2" s="2" t="inlineStr">
+      <c r="A2" t="inlineStr">
         <is>
           <t>TC-OTA-001</t>
         </is>
       </c>
-      <c r="B2" s="2" t="inlineStr">
+      <c r="B2" t="inlineStr">
         <is>
           <t>OtaTask.execute正常执行</t>
         </is>
       </c>
-      <c r="C2" s="2" t="inlineStr">
+      <c r="C2" t="inlineStr">
         <is>
           <t>P0</t>
         </is>
       </c>
-      <c r="D2" s="2" t="inlineStr">
+      <c r="D2" t="inlineStr">
         <is>
           <t>OtaTask实例已创建</t>
         </is>
       </c>
-      <c r="E2" s="2" t="inlineStr">
+      <c r="E2" t="inlineStr">
         <is>
           <t>1.调用OtaTask.execute()
 2.检查升级流程启动</t>
         </is>
       </c>
-      <c r="F2" s="2" t="inlineStr">
+      <c r="F2" t="inlineStr">
         <is>
           <t>升级流程正常启动，参数正确</t>
         </is>
       </c>
-      <c r="G2" s="2" t="inlineStr">
+      <c r="G2" t="inlineStr">
         <is>
           <t>单元测试</t>
         </is>
       </c>
-      <c r="H2" s="2" t="inlineStr">
+      <c r="H2" t="inlineStr">
         <is>
           <t>待执行</t>
         </is>
       </c>
     </row>
     <row r="3">
-      <c r="A3" s="2" t="inlineStr">
+      <c r="A3" t="inlineStr">
         <is>
           <t>TC-OTA-002</t>
         </is>
       </c>
-      <c r="B3" s="2" t="inlineStr">
+      <c r="B3" t="inlineStr">
         <is>
           <t>isRandom配置生效</t>
         </is>
       </c>
-      <c r="C3" s="2" t="inlineStr">
+      <c r="C3" t="inlineStr">
         <is>
           <t>P0</t>
         </is>
       </c>
-      <c r="D3" s="2" t="inlineStr">
+      <c r="D3" t="inlineStr">
         <is>
           <t>OtaTask.isRandom已设置</t>
         </is>
       </c>
-      <c r="E3" s="2" t="inlineStr">
+      <c r="E3" t="inlineStr">
         <is>
           <t>1.isRandom=true多次执行
 2.收集升级时间点
 3.isRandom=false再测试</t>
         </is>
       </c>
-      <c r="F3" s="2" t="inlineStr">
+      <c r="F3" t="inlineStr">
         <is>
           <t>true时升级时间随机；false时固定</t>
         </is>
       </c>
-      <c r="G3" s="2" t="inlineStr">
+      <c r="G3" t="inlineStr">
         <is>
           <t>单元测试</t>
         </is>
       </c>
-      <c r="H3" s="2" t="inlineStr">
+      <c r="H3" t="inlineStr">
         <is>
           <t>待执行</t>
         </is>
       </c>
     </row>
     <row r="4">
-      <c r="A4" s="2" t="inlineStr">
+      <c r="A4" t="inlineStr">
         <is>
           <t>TC-OTA-003</t>
         </is>
       </c>
-      <c r="B4" s="2" t="inlineStr">
+      <c r="B4" t="inlineStr">
         <is>
           <t>升级后清除鸡叫累计</t>
         </is>
       </c>
-      <c r="C4" s="2" t="inlineStr">
+      <c r="C4" t="inlineStr">
         <is>
           <t>P0</t>
         </is>
       </c>
-      <c r="D4" s="2" t="inlineStr">
+      <c r="D4" t="inlineStr">
         <is>
           <t>鸡叫累计&gt;0</t>
         </is>
       </c>
-      <c r="E4" s="2" t="inlineStr">
+      <c r="E4" t="inlineStr">
         <is>
           <t>1.设置鸡叫累计值&gt;0
 2.执行OtaTask
 3.检查鸡叫累计值</t>
         </is>
       </c>
-      <c r="F4" s="2" t="inlineStr">
+      <c r="F4" t="inlineStr">
         <is>
           <t>升级后鸡叫累计值归零</t>
         </is>
       </c>
-      <c r="G4" s="2" t="inlineStr">
+      <c r="G4" t="inlineStr">
         <is>
           <t>集成测试</t>
         </is>
       </c>
-      <c r="H4" s="2" t="inlineStr">
+      <c r="H4" t="inlineStr">
         <is>
           <t>待执行</t>
         </is>
       </c>
     </row>
     <row r="5">
-      <c r="A5" s="2" t="inlineStr">
+      <c r="A5" t="inlineStr">
         <is>
           <t>TC-OTA-004</t>
         </is>
       </c>
-      <c r="B5" s="2" t="inlineStr">
+      <c r="B5" t="inlineStr">
         <is>
           <t>升级后清除预约鸡叫</t>
         </is>
       </c>
-      <c r="C5" s="2" t="inlineStr">
+      <c r="C5" t="inlineStr">
         <is>
           <t>P0</t>
         </is>
       </c>
-      <c r="D5" s="2" t="inlineStr">
+      <c r="D5" t="inlineStr">
         <is>
           <t>有预约的鸡叫</t>
         </is>
       </c>
-      <c r="E5" s="2" t="inlineStr">
+      <c r="E5" t="inlineStr">
         <is>
           <t>1.预约一个鸡叫请求
 2.执行OtaTask
 3.检查预约队列</t>
         </is>
       </c>
-      <c r="F5" s="2" t="inlineStr">
+      <c r="F5" t="inlineStr">
         <is>
           <t>升级后预约鸡叫队列清空</t>
         </is>
       </c>
-      <c r="G5" s="2" t="inlineStr">
+      <c r="G5" t="inlineStr">
         <is>
           <t>集成测试</t>
         </is>
       </c>
-      <c r="H5" s="2" t="inlineStr">
+      <c r="H5" t="inlineStr">
         <is>
           <t>待执行</t>
         </is>
       </c>
     </row>
     <row r="6">
-      <c r="A6" s="2" t="inlineStr">
+      <c r="A6" t="inlineStr">
         <is>
           <t>TC-OTA-005</t>
         </is>
       </c>
-      <c r="B6" s="2" t="inlineStr">
+      <c r="B6" t="inlineStr">
         <is>
           <t>升级中CrowTask到达</t>
         </is>
       </c>
-      <c r="C6" s="2" t="inlineStr">
+      <c r="C6" t="inlineStr">
         <is>
           <t>P1</t>
         </is>
       </c>
-      <c r="D6" s="2" t="inlineStr">
+      <c r="D6" t="inlineStr">
         <is>
           <t>OtaTask正在执行</t>
         </is>
       </c>
-      <c r="E6" s="2" t="inlineStr">
+      <c r="E6" t="inlineStr">
         <is>
           <t>1.OtaTask启动
 2.CrowTask到达预定时间
 3.检查执行顺序</t>
         </is>
       </c>
-      <c r="F6" s="2" t="inlineStr">
+      <c r="F6" t="inlineStr">
         <is>
           <t>根据优先级决定是否打断</t>
         </is>
       </c>
-      <c r="G6" s="2" t="inlineStr">
+      <c r="G6" t="inlineStr">
         <is>
           <t>集成测试</t>
         </is>
       </c>
-      <c r="H6" s="2" t="inlineStr">
+      <c r="H6" t="inlineStr">
         <is>
           <t>待执行</t>
         </is>
       </c>
     </row>
     <row r="7">
-      <c r="A7" s="2" t="inlineStr">
+      <c r="A7" t="inlineStr">
         <is>
           <t>TC-OTA-006</t>
         </is>
       </c>
-      <c r="B7" s="2" t="inlineStr">
+      <c r="B7" t="inlineStr">
         <is>
           <t>设备离线时升级</t>
         </is>
       </c>
-      <c r="C7" s="2" t="inlineStr">
+      <c r="C7" t="inlineStr">
         <is>
           <t>P1</t>
         </is>
       </c>
-      <c r="D7" s="2" t="inlineStr">
+      <c r="D7" t="inlineStr">
         <is>
           <t>设备离线</t>
         </is>
       </c>
-      <c r="E7" s="2" t="inlineStr">
+      <c r="E7" t="inlineStr">
         <is>
           <t>1.模拟设备离线
 2.执行OtaTask</t>
         </is>
       </c>
-      <c r="F7" s="2" t="inlineStr">
+      <c r="F7" t="inlineStr">
         <is>
           <t>升级失败并记录离线日志</t>
         </is>
       </c>
-      <c r="G7" s="2" t="inlineStr">
+      <c r="G7" t="inlineStr">
         <is>
           <t>单元测试</t>
         </is>
       </c>
-      <c r="H7" s="2" t="inlineStr">
+      <c r="H7" t="inlineStr">
         <is>
           <t>待执行</t>
         </is>
       </c>
     </row>
     <row r="8">
-      <c r="A8" s="2" t="inlineStr">
+      <c r="A8" t="inlineStr">
         <is>
           <t>TC-OTA-007</t>
         </is>
       </c>
-      <c r="B8" s="2" t="inlineStr">
+      <c r="B8" t="inlineStr">
         <is>
           <t>重复升级跳过</t>
         </is>
       </c>
-      <c r="C8" s="2" t="inlineStr">
+      <c r="C8" t="inlineStr">
         <is>
           <t>P1</t>
         </is>
       </c>
-      <c r="D8" s="2" t="inlineStr">
+      <c r="D8" t="inlineStr">
         <is>
           <t>OtaTask已执行过</t>
         </is>
       </c>
-      <c r="E8" s="2" t="inlineStr">
+      <c r="E8" t="inlineStr">
         <is>
           <t>1.再次执行OtaTask
 2.检查是否重复</t>
         </is>
       </c>
-      <c r="F8" s="2" t="inlineStr">
+      <c r="F8" t="inlineStr">
         <is>
           <t>已有最新版本时跳过升级</t>
         </is>
       </c>
-      <c r="G8" s="2" t="inlineStr">
+      <c r="G8" t="inlineStr">
         <is>
           <t>单元测试</t>
         </is>
       </c>
-      <c r="H8" s="2" t="inlineStr">
+      <c r="H8" t="inlineStr">
         <is>
           <t>待执行</t>
         </is>
       </c>
     </row>
     <row r="9">
-      <c r="A9" s="2" t="inlineStr">
+      <c r="A9" t="inlineStr">
         <is>
           <t>TC-OTA-008</t>
         </is>
       </c>
-      <c r="B9" s="2" t="inlineStr">
+      <c r="B9" t="inlineStr">
         <is>
           <t>升级中系统重启</t>
         </is>
       </c>
-      <c r="C9" s="2" t="inlineStr">
+      <c r="C9" t="inlineStr">
         <is>
           <t>P2</t>
         </is>
       </c>
-      <c r="D9" s="2" t="inlineStr">
+      <c r="D9" t="inlineStr">
         <is>
           <t>OtaTask执行到一半</t>
         </is>
       </c>
-      <c r="E9" s="2" t="inlineStr">
+      <c r="E9" t="inlineStr">
         <is>
           <t>1.升级50%时重启
 2.重启后检查状态</t>
         </is>
       </c>
-      <c r="F9" s="2" t="inlineStr">
+      <c r="F9" t="inlineStr">
         <is>
           <t>重启后恢复或重新开始</t>
         </is>
       </c>
-      <c r="G9" s="2" t="inlineStr">
+      <c r="G9" t="inlineStr">
         <is>
           <t>集成测试</t>
         </is>
       </c>
-      <c r="H9" s="2" t="inlineStr">
+      <c r="H9" t="inlineStr">
         <is>
           <t>待执行</t>
         </is>
@@ -1759,476 +1759,476 @@
   </cols>
   <sheetData>
     <row r="1">
-      <c r="A1" s="1" t="inlineStr">
+      <c r="A1" t="inlineStr">
         <is>
           <t>用例ID</t>
         </is>
       </c>
-      <c r="B1" s="1" t="inlineStr">
+      <c r="B1" t="inlineStr">
         <is>
           <t>用例名称</t>
         </is>
       </c>
-      <c r="C1" s="1" t="inlineStr">
+      <c r="C1" t="inlineStr">
         <is>
           <t>优先级</t>
         </is>
       </c>
-      <c r="D1" s="1" t="inlineStr">
+      <c r="D1" t="inlineStr">
         <is>
           <t>前置条件</t>
         </is>
       </c>
-      <c r="E1" s="1" t="inlineStr">
+      <c r="E1" t="inlineStr">
         <is>
           <t>测试步骤</t>
         </is>
       </c>
-      <c r="F1" s="1" t="inlineStr">
+      <c r="F1" t="inlineStr">
         <is>
           <t>预期结果</t>
         </is>
       </c>
-      <c r="G1" s="1" t="inlineStr">
+      <c r="G1" t="inlineStr">
         <is>
           <t>测试类型</t>
         </is>
       </c>
-      <c r="H1" s="1" t="inlineStr">
+      <c r="H1" t="inlineStr">
         <is>
           <t>状态</t>
         </is>
       </c>
     </row>
     <row r="2">
-      <c r="A2" s="2" t="inlineStr">
+      <c r="A2" t="inlineStr">
         <is>
           <t>TC-CROW-001</t>
         </is>
       </c>
-      <c r="B2" s="2" t="inlineStr">
+      <c r="B2" t="inlineStr">
         <is>
           <t>scheduleNextCrow正常调度</t>
         </is>
       </c>
-      <c r="C2" s="2" t="inlineStr">
+      <c r="C2" t="inlineStr">
         <is>
           <t>P0</t>
         </is>
       </c>
-      <c r="D2" s="2" t="inlineStr">
+      <c r="D2" t="inlineStr">
         <is>
           <t>CrowTask实例已创建</t>
         </is>
       </c>
-      <c r="E2" s="2" t="inlineStr">
+      <c r="E2" t="inlineStr">
         <is>
           <t>1.设置intervalDays=7
 2.scheduleNextCrow()
 3.检查下次时间</t>
         </is>
       </c>
-      <c r="F2" s="2" t="inlineStr">
+      <c r="F2" t="inlineStr">
         <is>
           <t>下次鸡叫=当前+7天，2:00-4:00间</t>
         </is>
       </c>
-      <c r="G2" s="2" t="inlineStr">
+      <c r="G2" t="inlineStr">
         <is>
           <t>单元测试</t>
         </is>
       </c>
-      <c r="H2" s="2" t="inlineStr">
+      <c r="H2" t="inlineStr">
         <is>
           <t>待执行</t>
         </is>
       </c>
     </row>
     <row r="3">
-      <c r="A3" s="2" t="inlineStr">
+      <c r="A3" t="inlineStr">
         <is>
           <t>TC-CROW-002</t>
         </is>
       </c>
-      <c r="B3" s="2" t="inlineStr">
+      <c r="B3" t="inlineStr">
         <is>
           <t>鸡叫时间窗口2:00-4:00</t>
         </is>
       </c>
-      <c r="C3" s="2" t="inlineStr">
+      <c r="C3" t="inlineStr">
         <is>
           <t>P0</t>
         </is>
       </c>
-      <c r="D3" s="2" t="inlineStr">
+      <c r="D3" t="inlineStr">
         <is>
           <t>CrowTask已调度</t>
         </is>
       </c>
-      <c r="E3" s="2" t="inlineStr">
+      <c r="E3" t="inlineStr">
         <is>
           <t>1.到达间隔时间触发
 2.多次检查实际时间</t>
         </is>
       </c>
-      <c r="F3" s="2" t="inlineStr">
+      <c r="F3" t="inlineStr">
         <is>
           <t>每次在2:00-4:00范围内随机</t>
         </is>
       </c>
-      <c r="G3" s="2" t="inlineStr">
+      <c r="G3" t="inlineStr">
         <is>
           <t>单元测试</t>
         </is>
       </c>
-      <c r="H3" s="2" t="inlineStr">
+      <c r="H3" t="inlineStr">
         <is>
           <t>待执行</t>
         </is>
       </c>
     </row>
     <row r="4">
-      <c r="A4" s="2" t="inlineStr">
+      <c r="A4" t="inlineStr">
         <is>
           <t>TC-CROW-003</t>
         </is>
       </c>
-      <c r="B4" s="2" t="inlineStr">
+      <c r="B4" t="inlineStr">
         <is>
           <t>鸡叫不可打断验证</t>
         </is>
       </c>
-      <c r="C4" s="2" t="inlineStr">
+      <c r="C4" t="inlineStr">
         <is>
           <t>P0</t>
         </is>
       </c>
-      <c r="D4" s="2" t="inlineStr">
+      <c r="D4" t="inlineStr">
         <is>
           <t>CrowTask正在鸡叫</t>
         </is>
       </c>
-      <c r="E4" s="2" t="inlineStr">
+      <c r="E4" t="inlineStr">
         <is>
           <t>1.鸡叫中
 2.SentinelTask尝试打断
 3.OtaTask尝试打断</t>
         </is>
       </c>
-      <c r="F4" s="2" t="inlineStr">
+      <c r="F4" t="inlineStr">
         <is>
           <t>鸡叫不接受打断请求</t>
         </is>
       </c>
-      <c r="G4" s="2" t="inlineStr">
+      <c r="G4" t="inlineStr">
         <is>
           <t>集成测试</t>
         </is>
       </c>
-      <c r="H4" s="2" t="inlineStr">
+      <c r="H4" t="inlineStr">
         <is>
           <t>待执行</t>
         </is>
       </c>
     </row>
     <row r="5">
-      <c r="A5" s="2" t="inlineStr">
+      <c r="A5" t="inlineStr">
         <is>
           <t>TC-CROW-004</t>
         </is>
       </c>
-      <c r="B5" s="2" t="inlineStr">
+      <c r="B5" t="inlineStr">
         <is>
           <t>clearCrowFlag清除标志</t>
         </is>
       </c>
-      <c r="C5" s="2" t="inlineStr">
+      <c r="C5" t="inlineStr">
         <is>
           <t>P0</t>
         </is>
       </c>
-      <c r="D5" s="2" t="inlineStr">
+      <c r="D5" t="inlineStr">
         <is>
           <t>crowFlag=True</t>
         </is>
       </c>
-      <c r="E5" s="2" t="inlineStr">
+      <c r="E5" t="inlineStr">
         <is>
           <t>1.调用clearCrowFlag()
 2.检查crowFlag</t>
         </is>
       </c>
-      <c r="F5" s="2" t="inlineStr">
+      <c r="F5" t="inlineStr">
         <is>
           <t>crowFlag变为false</t>
         </is>
       </c>
-      <c r="G5" s="2" t="inlineStr">
+      <c r="G5" t="inlineStr">
         <is>
           <t>单元测试</t>
         </is>
       </c>
-      <c r="H5" s="2" t="inlineStr">
+      <c r="H5" t="inlineStr">
         <is>
           <t>待执行</t>
         </is>
       </c>
     </row>
     <row r="6">
-      <c r="A6" s="2" t="inlineStr">
+      <c r="A6" t="inlineStr">
         <is>
           <t>TC-CROW-005</t>
         </is>
       </c>
-      <c r="B6" s="2" t="inlineStr">
+      <c r="B6" t="inlineStr">
         <is>
           <t>间隔天数边界值</t>
         </is>
       </c>
-      <c r="C6" s="2" t="inlineStr">
+      <c r="C6" t="inlineStr">
         <is>
           <t>P0</t>
         </is>
       </c>
-      <c r="D6" s="2" t="inlineStr">
+      <c r="D6" t="inlineStr">
         <is>
           <t>CrowTask已创建</t>
         </is>
       </c>
-      <c r="E6" s="2" t="inlineStr">
+      <c r="E6" t="inlineStr">
         <is>
           <t>1.intervalDays=0
 2.intervalDays=1
 3.intervalDays=365</t>
         </is>
       </c>
-      <c r="F6" s="2" t="inlineStr">
+      <c r="F6" t="inlineStr">
         <is>
           <t>0立即执行；1和365正常</t>
         </is>
       </c>
-      <c r="G6" s="2" t="inlineStr">
+      <c r="G6" t="inlineStr">
         <is>
           <t>单元测试</t>
         </is>
       </c>
-      <c r="H6" s="2" t="inlineStr">
+      <c r="H6" t="inlineStr">
         <is>
           <t>待执行</t>
         </is>
       </c>
     </row>
     <row r="7">
-      <c r="A7" s="2" t="inlineStr">
+      <c r="A7" t="inlineStr">
         <is>
           <t>TC-CROW-006</t>
         </is>
       </c>
-      <c r="B7" s="2" t="inlineStr">
+      <c r="B7" t="inlineStr">
         <is>
           <t>scheduledTime受保护</t>
         </is>
       </c>
-      <c r="C7" s="2" t="inlineStr">
+      <c r="C7" t="inlineStr">
         <is>
           <t>P1</t>
         </is>
       </c>
-      <c r="D7" s="2" t="inlineStr">
+      <c r="D7" t="inlineStr">
         <is>
           <t>CrowTask已创建</t>
         </is>
       </c>
-      <c r="E7" s="2" t="inlineStr">
+      <c r="E7" t="inlineStr">
         <is>
           <t>1.外部代码访问scheduledTime
 2.子类代码访问</t>
         </is>
       </c>
-      <c r="F7" s="2" t="inlineStr">
+      <c r="F7" t="inlineStr">
         <is>
           <t>外部不可访问；子类可访问</t>
         </is>
       </c>
-      <c r="G7" s="2" t="inlineStr">
+      <c r="G7" t="inlineStr">
         <is>
           <t>单元测试</t>
         </is>
       </c>
-      <c r="H7" s="2" t="inlineStr">
+      <c r="H7" t="inlineStr">
         <is>
           <t>待执行</t>
         </is>
       </c>
     </row>
     <row r="8">
-      <c r="A8" s="2" t="inlineStr">
+      <c r="A8" t="inlineStr">
         <is>
           <t>TC-CROW-007</t>
         </is>
       </c>
-      <c r="B8" s="2" t="inlineStr">
+      <c r="B8" t="inlineStr">
         <is>
           <t>鸡叫与升级同时</t>
         </is>
       </c>
-      <c r="C8" s="2" t="inlineStr">
+      <c r="C8" t="inlineStr">
         <is>
           <t>P1</t>
         </is>
       </c>
-      <c r="D8" s="2" t="inlineStr">
+      <c r="D8" t="inlineStr">
         <is>
           <t>鸡叫+升级同时触发</t>
         </is>
       </c>
-      <c r="E8" s="2" t="inlineStr">
+      <c r="E8" t="inlineStr">
         <is>
           <t>1.同时触发
 2.检查执行顺序</t>
         </is>
       </c>
-      <c r="F8" s="2" t="inlineStr">
+      <c r="F8" t="inlineStr">
         <is>
           <t>鸡叫优先执行</t>
         </is>
       </c>
-      <c r="G8" s="2" t="inlineStr">
+      <c r="G8" t="inlineStr">
         <is>
           <t>集成测试</t>
         </is>
       </c>
-      <c r="H8" s="2" t="inlineStr">
+      <c r="H8" t="inlineStr">
         <is>
           <t>待执行</t>
         </is>
       </c>
     </row>
     <row r="9">
-      <c r="A9" s="2" t="inlineStr">
+      <c r="A9" t="inlineStr">
         <is>
           <t>TC-CROW-008</t>
         </is>
       </c>
-      <c r="B9" s="2" t="inlineStr">
+      <c r="B9" t="inlineStr">
         <is>
           <t>预约鸡叫被清除</t>
         </is>
       </c>
-      <c r="C9" s="2" t="inlineStr">
+      <c r="C9" t="inlineStr">
         <is>
           <t>P1</t>
         </is>
       </c>
-      <c r="D9" s="2" t="inlineStr">
+      <c r="D9" t="inlineStr">
         <is>
           <t>有预约的鸡叫</t>
         </is>
       </c>
-      <c r="E9" s="2" t="inlineStr">
+      <c r="E9" t="inlineStr">
         <is>
           <t>1.调用clearScheduledCrow
 2.等待原鸡叫时间</t>
         </is>
       </c>
-      <c r="F9" s="2" t="inlineStr">
+      <c r="F9" t="inlineStr">
         <is>
           <t>鸡叫不再执行</t>
         </is>
       </c>
-      <c r="G9" s="2" t="inlineStr">
+      <c r="G9" t="inlineStr">
         <is>
           <t>单元测试</t>
         </is>
       </c>
-      <c r="H9" s="2" t="inlineStr">
+      <c r="H9" t="inlineStr">
         <is>
           <t>待执行</t>
         </is>
       </c>
     </row>
     <row r="10">
-      <c r="A10" s="2" t="inlineStr">
+      <c r="A10" t="inlineStr">
         <is>
           <t>TC-CROW-009</t>
         </is>
       </c>
-      <c r="B10" s="2" t="inlineStr">
+      <c r="B10" t="inlineStr">
         <is>
           <t>鸡叫累计值管理</t>
         </is>
       </c>
-      <c r="C10" s="2" t="inlineStr">
+      <c r="C10" t="inlineStr">
         <is>
           <t>P2</t>
         </is>
       </c>
-      <c r="D10" s="2" t="inlineStr">
+      <c r="D10" t="inlineStr">
         <is>
           <t>系统有鸡叫累计</t>
         </is>
       </c>
-      <c r="E10" s="2" t="inlineStr">
+      <c r="E10" t="inlineStr">
         <is>
           <t>1.多次触发鸡叫
 2.检查累计值
 3.清除累计</t>
         </is>
       </c>
-      <c r="F10" s="2" t="inlineStr">
+      <c r="F10" t="inlineStr">
         <is>
           <t>累计正确递增，可清除</t>
         </is>
       </c>
-      <c r="G10" s="2" t="inlineStr">
+      <c r="G10" t="inlineStr">
         <is>
           <t>单元测试</t>
         </is>
       </c>
-      <c r="H10" s="2" t="inlineStr">
+      <c r="H10" t="inlineStr">
         <is>
           <t>待执行</t>
         </is>
       </c>
     </row>
     <row r="11">
-      <c r="A11" s="2" t="inlineStr">
+      <c r="A11" t="inlineStr">
         <is>
           <t>TC-CROW-010</t>
         </is>
       </c>
-      <c r="B11" s="2" t="inlineStr">
+      <c r="B11" t="inlineStr">
         <is>
           <t>跨天调度</t>
         </is>
       </c>
-      <c r="C11" s="2" t="inlineStr">
+      <c r="C11" t="inlineStr">
         <is>
           <t>P2</t>
         </is>
       </c>
-      <c r="D11" s="2" t="inlineStr">
-        <is>
-          <t>间隔7天</t>
-        </is>
-      </c>
-      <c r="E11" s="2" t="inlineStr">
+      <c r="D11" t="inlineStr">
+        <is>
+          <t>距离上次鸡叫间隔7天</t>
+        </is>
+      </c>
+      <c r="E11" t="inlineStr">
         <is>
           <t>1.模拟跨23:59:59
 2.检查调度</t>
         </is>
       </c>
-      <c r="F11" s="2" t="inlineStr">
+      <c r="F11" t="inlineStr">
         <is>
           <t>跨天后时间计算正确</t>
         </is>
       </c>
-      <c r="G11" s="2" t="inlineStr">
+      <c r="G11" t="inlineStr">
         <is>
           <t>单元测试</t>
         </is>
       </c>
-      <c r="H11" s="2" t="inlineStr">
+      <c r="H11" t="inlineStr">
         <is>
           <t>待执行</t>
         </is>
@@ -2259,433 +2259,433 @@
   </cols>
   <sheetData>
     <row r="1">
-      <c r="A1" s="1" t="inlineStr">
+      <c r="A1" t="inlineStr">
         <is>
           <t>用例ID</t>
         </is>
       </c>
-      <c r="B1" s="1" t="inlineStr">
+      <c r="B1" t="inlineStr">
         <is>
           <t>用例名称</t>
         </is>
       </c>
-      <c r="C1" s="1" t="inlineStr">
+      <c r="C1" t="inlineStr">
         <is>
           <t>优先级</t>
         </is>
       </c>
-      <c r="D1" s="1" t="inlineStr">
+      <c r="D1" t="inlineStr">
         <is>
           <t>前置条件</t>
         </is>
       </c>
-      <c r="E1" s="1" t="inlineStr">
+      <c r="E1" t="inlineStr">
         <is>
           <t>测试步骤</t>
         </is>
       </c>
-      <c r="F1" s="1" t="inlineStr">
+      <c r="F1" t="inlineStr">
         <is>
           <t>预期结果</t>
         </is>
       </c>
-      <c r="G1" s="1" t="inlineStr">
+      <c r="G1" t="inlineStr">
         <is>
           <t>测试类型</t>
         </is>
       </c>
-      <c r="H1" s="1" t="inlineStr">
+      <c r="H1" t="inlineStr">
         <is>
           <t>状态</t>
         </is>
       </c>
     </row>
     <row r="2">
-      <c r="A2" s="2" t="inlineStr">
+      <c r="A2" t="inlineStr">
         <is>
           <t>TC-SEN-001</t>
         </is>
       </c>
-      <c r="B2" s="2" t="inlineStr">
+      <c r="B2" t="inlineStr">
         <is>
           <t>哨兵正常执行</t>
         </is>
       </c>
-      <c r="C2" s="2" t="inlineStr">
+      <c r="C2" t="inlineStr">
         <is>
           <t>P0</t>
         </is>
       </c>
-      <c r="D2" s="2" t="inlineStr">
+      <c r="D2" t="inlineStr">
         <is>
           <t>SentinelTask已创建</t>
         </is>
       </c>
-      <c r="E2" s="2" t="inlineStr">
+      <c r="E2" t="inlineStr">
         <is>
           <t>1.调用execute()
 2.检查isRunning</t>
         </is>
       </c>
-      <c r="F2" s="2" t="inlineStr">
+      <c r="F2" t="inlineStr">
         <is>
           <t>isRunning=true</t>
         </is>
       </c>
-      <c r="G2" s="2" t="inlineStr">
+      <c r="G2" t="inlineStr">
         <is>
           <t>单元测试</t>
         </is>
       </c>
-      <c r="H2" s="2" t="inlineStr">
+      <c r="H2" t="inlineStr">
         <is>
           <t>待执行</t>
         </is>
       </c>
     </row>
     <row r="3">
-      <c r="A3" s="2" t="inlineStr">
+      <c r="A3" t="inlineStr">
         <is>
           <t>TC-SEN-002</t>
         </is>
       </c>
-      <c r="B3" s="2" t="inlineStr">
+      <c r="B3" t="inlineStr">
         <is>
           <t>哨兵被CrowTask打断</t>
         </is>
       </c>
-      <c r="C3" s="2" t="inlineStr">
+      <c r="C3" t="inlineStr">
         <is>
           <t>P0</t>
         </is>
       </c>
-      <c r="D3" s="2" t="inlineStr">
+      <c r="D3" t="inlineStr">
         <is>
           <t>哨兵正在执行</t>
         </is>
       </c>
-      <c r="E3" s="2" t="inlineStr">
+      <c r="E3" t="inlineStr">
         <is>
           <t>1.SentinelTask.execute()
 2.CrowTask触发
 3.检查isRunning+interruptedBy</t>
         </is>
       </c>
-      <c r="F3" s="2" t="inlineStr">
+      <c r="F3" t="inlineStr">
         <is>
           <t>isRunning=false, interruptedBy=CrowTask</t>
         </is>
       </c>
-      <c r="G3" s="2" t="inlineStr">
+      <c r="G3" t="inlineStr">
         <is>
           <t>集成测试</t>
         </is>
       </c>
-      <c r="H3" s="2" t="inlineStr">
+      <c r="H3" t="inlineStr">
         <is>
           <t>待执行</t>
         </is>
       </c>
     </row>
     <row r="4">
-      <c r="A4" s="2" t="inlineStr">
+      <c r="A4" t="inlineStr">
         <is>
           <t>TC-SEN-003</t>
         </is>
       </c>
-      <c r="B4" s="2" t="inlineStr">
+      <c r="B4" t="inlineStr">
         <is>
           <t>哨兵被OtaTask打断</t>
         </is>
       </c>
-      <c r="C4" s="2" t="inlineStr">
+      <c r="C4" t="inlineStr">
         <is>
           <t>P0</t>
         </is>
       </c>
-      <c r="D4" s="2" t="inlineStr">
+      <c r="D4" t="inlineStr">
         <is>
           <t>哨兵正在执行</t>
         </is>
       </c>
-      <c r="E4" s="2" t="inlineStr">
+      <c r="E4" t="inlineStr">
         <is>
           <t>1.SentinelTask.execute()
 2.OtaTask触发
 3.检查打断状态</t>
         </is>
       </c>
-      <c r="F4" s="2" t="inlineStr">
+      <c r="F4" t="inlineStr">
         <is>
           <t>哨兵被打断，状态正确保存</t>
         </is>
       </c>
-      <c r="G4" s="2" t="inlineStr">
+      <c r="G4" t="inlineStr">
         <is>
           <t>集成测试</t>
         </is>
       </c>
-      <c r="H4" s="2" t="inlineStr">
+      <c r="H4" t="inlineStr">
         <is>
           <t>待执行</t>
         </is>
       </c>
     </row>
     <row r="5">
-      <c r="A5" s="2" t="inlineStr">
+      <c r="A5" t="inlineStr">
         <is>
           <t>TC-SEN-004</t>
         </is>
       </c>
-      <c r="B5" s="2" t="inlineStr">
+      <c r="B5" t="inlineStr">
         <is>
           <t>哨兵恢复执行resume()</t>
         </is>
       </c>
-      <c r="C5" s="2" t="inlineStr">
+      <c r="C5" t="inlineStr">
         <is>
           <t>P0</t>
         </is>
       </c>
-      <c r="D5" s="2" t="inlineStr">
+      <c r="D5" t="inlineStr">
         <is>
           <t>哨兵被打断后</t>
         </is>
       </c>
-      <c r="E5" s="2" t="inlineStr">
+      <c r="E5" t="inlineStr">
         <is>
           <t>1.打断任务完成
 2.调用resume()
 3.检查isRunning</t>
         </is>
       </c>
-      <c r="F5" s="2" t="inlineStr">
+      <c r="F5" t="inlineStr">
         <is>
           <t>isRunning恢复true，之前状态恢复</t>
         </is>
       </c>
-      <c r="G5" s="2" t="inlineStr">
+      <c r="G5" t="inlineStr">
         <is>
           <t>单元测试</t>
         </is>
       </c>
-      <c r="H5" s="2" t="inlineStr">
+      <c r="H5" t="inlineStr">
         <is>
           <t>待执行</t>
         </is>
       </c>
     </row>
     <row r="6">
-      <c r="A6" s="2" t="inlineStr">
+      <c r="A6" t="inlineStr">
         <is>
           <t>TC-SEN-005</t>
         </is>
       </c>
-      <c r="B6" s="2" t="inlineStr">
+      <c r="B6" t="inlineStr">
         <is>
           <t>未运行时打断信号</t>
         </is>
       </c>
-      <c r="C6" s="2" t="inlineStr">
+      <c r="C6" t="inlineStr">
         <is>
           <t>P1</t>
         </is>
       </c>
-      <c r="D6" s="2" t="inlineStr">
+      <c r="D6" t="inlineStr">
         <is>
           <t>哨兵未启动</t>
         </is>
       </c>
-      <c r="E6" s="2" t="inlineStr">
+      <c r="E6" t="inlineStr">
         <is>
           <t>1.调用interrupt()
 2.检查状态</t>
         </is>
       </c>
-      <c r="F6" s="2" t="inlineStr">
+      <c r="F6" t="inlineStr">
         <is>
           <t>打断被忽略，isRunning仍为false</t>
         </is>
       </c>
-      <c r="G6" s="2" t="inlineStr">
+      <c r="G6" t="inlineStr">
         <is>
           <t>单元测试</t>
         </is>
       </c>
-      <c r="H6" s="2" t="inlineStr">
+      <c r="H6" t="inlineStr">
         <is>
           <t>待执行</t>
         </is>
       </c>
     </row>
     <row r="7">
-      <c r="A7" s="2" t="inlineStr">
+      <c r="A7" t="inlineStr">
         <is>
           <t>TC-SEN-006</t>
         </is>
       </c>
-      <c r="B7" s="2" t="inlineStr">
+      <c r="B7" t="inlineStr">
         <is>
           <t>多次打断+恢复</t>
         </is>
       </c>
-      <c r="C7" s="2" t="inlineStr">
+      <c r="C7" t="inlineStr">
         <is>
           <t>P1</t>
         </is>
       </c>
-      <c r="D7" s="2" t="inlineStr">
+      <c r="D7" t="inlineStr">
         <is>
           <t>哨兵反复被打断</t>
         </is>
       </c>
-      <c r="E7" s="2" t="inlineStr">
+      <c r="E7" t="inlineStr">
         <is>
           <t>1.打断-&gt;恢复 重复3次
 2.检查状态</t>
         </is>
       </c>
-      <c r="F7" s="2" t="inlineStr">
+      <c r="F7" t="inlineStr">
         <is>
           <t>每次恢复后状态正确，无残留</t>
         </is>
       </c>
-      <c r="G7" s="2" t="inlineStr">
+      <c r="G7" t="inlineStr">
         <is>
           <t>单元测试</t>
         </is>
       </c>
-      <c r="H7" s="2" t="inlineStr">
+      <c r="H7" t="inlineStr">
         <is>
           <t>待执行</t>
         </is>
       </c>
     </row>
     <row r="8">
-      <c r="A8" s="2" t="inlineStr">
+      <c r="A8" t="inlineStr">
         <is>
           <t>TC-SEN-007</t>
         </is>
       </c>
-      <c r="B8" s="2" t="inlineStr">
+      <c r="B8" t="inlineStr">
         <is>
           <t>优先级打断规则</t>
         </is>
       </c>
-      <c r="C8" s="2" t="inlineStr">
+      <c r="C8" t="inlineStr">
         <is>
           <t>P1</t>
         </is>
       </c>
-      <c r="D8" s="2" t="inlineStr">
+      <c r="D8" t="inlineStr">
         <is>
           <t>多种任务并存</t>
         </is>
       </c>
-      <c r="E8" s="2" t="inlineStr">
+      <c r="E8" t="inlineStr">
         <is>
           <t>1.高/同/低优任务到达
 2.检查是否打断</t>
         </is>
       </c>
-      <c r="F8" s="2" t="inlineStr">
+      <c r="F8" t="inlineStr">
         <is>
           <t>高优打断；同优FIFO；低优等待</t>
         </is>
       </c>
-      <c r="G8" s="2" t="inlineStr">
+      <c r="G8" t="inlineStr">
         <is>
           <t>集成测试</t>
         </is>
       </c>
-      <c r="H8" s="2" t="inlineStr">
+      <c r="H8" t="inlineStr">
         <is>
           <t>待执行</t>
         </is>
       </c>
     </row>
     <row r="9">
-      <c r="A9" s="2" t="inlineStr">
+      <c r="A9" t="inlineStr">
         <is>
           <t>TC-SEN-008</t>
         </is>
       </c>
-      <c r="B9" s="2" t="inlineStr">
+      <c r="B9" t="inlineStr">
         <is>
           <t>打断异常后恢复</t>
         </is>
       </c>
-      <c r="C9" s="2" t="inlineStr">
+      <c r="C9" t="inlineStr">
         <is>
           <t>P2</t>
         </is>
       </c>
-      <c r="D9" s="2" t="inlineStr">
+      <c r="D9" t="inlineStr">
         <is>
           <t>哨兵被打断</t>
         </is>
       </c>
-      <c r="E9" s="2" t="inlineStr">
+      <c r="E9" t="inlineStr">
         <is>
           <t>1.打断任务抛异常
 2.检查哨兵
 3.resume()</t>
         </is>
       </c>
-      <c r="F9" s="2" t="inlineStr">
+      <c r="F9" t="inlineStr">
         <is>
           <t>异常不影响哨兵状态恢复</t>
         </is>
       </c>
-      <c r="G9" s="2" t="inlineStr">
+      <c r="G9" t="inlineStr">
         <is>
           <t>集成测试</t>
         </is>
       </c>
-      <c r="H9" s="2" t="inlineStr">
+      <c r="H9" t="inlineStr">
         <is>
           <t>待执行</t>
         </is>
       </c>
     </row>
     <row r="10">
-      <c r="A10" s="2" t="inlineStr">
+      <c r="A10" t="inlineStr">
         <is>
           <t>TC-SEN-009</t>
         </is>
       </c>
-      <c r="B10" s="2" t="inlineStr">
+      <c r="B10" t="inlineStr">
         <is>
           <t>interruptedBy封装</t>
         </is>
       </c>
-      <c r="C10" s="2" t="inlineStr">
+      <c r="C10" t="inlineStr">
         <is>
           <t>P2</t>
         </is>
       </c>
-      <c r="D10" s="2" t="inlineStr">
+      <c r="D10" t="inlineStr">
         <is>
           <t>哨兵被打断</t>
         </is>
       </c>
-      <c r="E10" s="2" t="inlineStr">
+      <c r="E10" t="inlineStr">
         <is>
           <t>1.外部直接修改interruptedBy
 2.检查</t>
         </is>
       </c>
-      <c r="F10" s="2" t="inlineStr">
+      <c r="F10" t="inlineStr">
         <is>
           <t>外部不可直接修改(private)</t>
         </is>
       </c>
-      <c r="G10" s="2" t="inlineStr">
+      <c r="G10" t="inlineStr">
         <is>
           <t>单元测试</t>
         </is>
       </c>
-      <c r="H10" s="2" t="inlineStr">
+      <c r="H10" t="inlineStr">
         <is>
           <t>待执行</t>
         </is>
@@ -2716,515 +2716,515 @@
   </cols>
   <sheetData>
     <row r="1">
-      <c r="A1" s="1" t="inlineStr">
+      <c r="A1" t="inlineStr">
         <is>
           <t>用例ID</t>
         </is>
       </c>
-      <c r="B1" s="1" t="inlineStr">
+      <c r="B1" t="inlineStr">
         <is>
           <t>用例名称</t>
         </is>
       </c>
-      <c r="C1" s="1" t="inlineStr">
+      <c r="C1" t="inlineStr">
         <is>
           <t>优先级</t>
         </is>
       </c>
-      <c r="D1" s="1" t="inlineStr">
+      <c r="D1" t="inlineStr">
         <is>
           <t>前置条件</t>
         </is>
       </c>
-      <c r="E1" s="1" t="inlineStr">
+      <c r="E1" t="inlineStr">
         <is>
           <t>测试步骤</t>
         </is>
       </c>
-      <c r="F1" s="1" t="inlineStr">
+      <c r="F1" t="inlineStr">
         <is>
           <t>预期结果</t>
         </is>
       </c>
-      <c r="G1" s="1" t="inlineStr">
+      <c r="G1" t="inlineStr">
         <is>
           <t>测试类型</t>
         </is>
       </c>
-      <c r="H1" s="1" t="inlineStr">
+      <c r="H1" t="inlineStr">
         <is>
           <t>状态</t>
         </is>
       </c>
     </row>
     <row r="2">
-      <c r="A2" s="2" t="inlineStr">
+      <c r="A2" t="inlineStr">
         <is>
           <t>TC-SCH-001</t>
         </is>
       </c>
-      <c r="B2" s="2" t="inlineStr">
+      <c r="B2" t="inlineStr">
         <is>
           <t>addTask添加任务</t>
         </is>
       </c>
-      <c r="C2" s="2" t="inlineStr">
+      <c r="C2" t="inlineStr">
         <is>
           <t>P0</t>
         </is>
       </c>
-      <c r="D2" s="2" t="inlineStr">
+      <c r="D2" t="inlineStr">
         <is>
           <t>TaskScheduler初始化</t>
         </is>
       </c>
-      <c r="E2" s="2" t="inlineStr">
+      <c r="E2" t="inlineStr">
         <is>
           <t>1.addTask(OtaTask)
 2.addTask(CrowTask)
 3.检查taskList</t>
         </is>
       </c>
-      <c r="F2" s="2" t="inlineStr">
+      <c r="F2" t="inlineStr">
         <is>
           <t>taskList长度=2</t>
         </is>
       </c>
-      <c r="G2" s="2" t="inlineStr">
+      <c r="G2" t="inlineStr">
         <is>
           <t>单元测试</t>
         </is>
       </c>
-      <c r="H2" s="2" t="inlineStr">
+      <c r="H2" t="inlineStr">
         <is>
           <t>待执行</t>
         </is>
       </c>
     </row>
     <row r="3">
-      <c r="A3" s="2" t="inlineStr">
+      <c r="A3" t="inlineStr">
         <is>
           <t>TC-SCH-002</t>
         </is>
       </c>
-      <c r="B3" s="2" t="inlineStr">
+      <c r="B3" t="inlineStr">
         <is>
           <t>removeTask删除任务</t>
         </is>
       </c>
-      <c r="C3" s="2" t="inlineStr">
+      <c r="C3" t="inlineStr">
         <is>
           <t>P0</t>
         </is>
       </c>
-      <c r="D3" s="2" t="inlineStr">
+      <c r="D3" t="inlineStr">
         <is>
           <t>taskList有2个任务</t>
         </is>
       </c>
-      <c r="E3" s="2" t="inlineStr">
+      <c r="E3" t="inlineStr">
         <is>
           <t>1.removeTask(OtaTask.id)
 2.检查taskList</t>
         </is>
       </c>
-      <c r="F3" s="2" t="inlineStr">
+      <c r="F3" t="inlineStr">
         <is>
           <t>OtaTask被移除</t>
         </is>
       </c>
-      <c r="G3" s="2" t="inlineStr">
+      <c r="G3" t="inlineStr">
         <is>
           <t>单元测试</t>
         </is>
       </c>
-      <c r="H3" s="2" t="inlineStr">
+      <c r="H3" t="inlineStr">
         <is>
           <t>待执行</t>
         </is>
       </c>
     </row>
     <row r="4">
-      <c r="A4" s="2" t="inlineStr">
+      <c r="A4" t="inlineStr">
         <is>
           <t>TC-SCH-003</t>
         </is>
       </c>
-      <c r="B4" s="2" t="inlineStr">
+      <c r="B4" t="inlineStr">
         <is>
           <t>按优先级排序执行</t>
         </is>
       </c>
-      <c r="C4" s="2" t="inlineStr">
+      <c r="C4" t="inlineStr">
         <is>
           <t>P0</t>
         </is>
       </c>
-      <c r="D4" s="2" t="inlineStr">
+      <c r="D4" t="inlineStr">
         <is>
           <t>不同优先级任务各1</t>
         </is>
       </c>
-      <c r="E4" s="2" t="inlineStr">
+      <c r="E4" t="inlineStr">
         <is>
           <t>1.添加P0/P1/P2任务
 2.executeTasks()
 3.记录顺序</t>
         </is>
       </c>
-      <c r="F4" s="2" t="inlineStr">
+      <c r="F4" t="inlineStr">
         <is>
           <t>P0-&gt;P1-&gt;P2顺序执行</t>
         </is>
       </c>
-      <c r="G4" s="2" t="inlineStr">
+      <c r="G4" t="inlineStr">
         <is>
           <t>单元测试</t>
         </is>
       </c>
-      <c r="H4" s="2" t="inlineStr">
+      <c r="H4" t="inlineStr">
         <is>
           <t>待执行</t>
         </is>
       </c>
     </row>
     <row r="5">
-      <c r="A5" s="2" t="inlineStr">
+      <c r="A5" t="inlineStr">
         <is>
           <t>TC-SCH-004</t>
         </is>
       </c>
-      <c r="B5" s="2" t="inlineStr">
+      <c r="B5" t="inlineStr">
         <is>
           <t>空列表执行</t>
         </is>
       </c>
-      <c r="C5" s="2" t="inlineStr">
+      <c r="C5" t="inlineStr">
         <is>
           <t>P0</t>
         </is>
       </c>
-      <c r="D5" s="2" t="inlineStr">
+      <c r="D5" t="inlineStr">
         <is>
           <t>taskList为空</t>
         </is>
       </c>
-      <c r="E5" s="2" t="inlineStr">
+      <c r="E5" t="inlineStr">
         <is>
           <t>1.调用executeTasks()</t>
         </is>
       </c>
-      <c r="F5" s="2" t="inlineStr">
+      <c r="F5" t="inlineStr">
         <is>
           <t>不抛异常，正常返回</t>
         </is>
       </c>
-      <c r="G5" s="2" t="inlineStr">
+      <c r="G5" t="inlineStr">
         <is>
           <t>单元测试</t>
         </is>
       </c>
-      <c r="H5" s="2" t="inlineStr">
+      <c r="H5" t="inlineStr">
         <is>
           <t>待执行</t>
         </is>
       </c>
     </row>
     <row r="6">
-      <c r="A6" s="2" t="inlineStr">
+      <c r="A6" t="inlineStr">
         <is>
           <t>TC-SCH-005</t>
         </is>
       </c>
-      <c r="B6" s="2" t="inlineStr">
+      <c r="B6" t="inlineStr">
         <is>
           <t>执行中动态添加</t>
         </is>
       </c>
-      <c r="C6" s="2" t="inlineStr">
+      <c r="C6" t="inlineStr">
         <is>
           <t>P0</t>
         </is>
       </c>
-      <c r="D6" s="2" t="inlineStr">
+      <c r="D6" t="inlineStr">
         <is>
           <t>executeTasks()执行中</t>
         </is>
       </c>
-      <c r="E6" s="2" t="inlineStr">
+      <c r="E6" t="inlineStr">
         <is>
           <t>1.执行中添加新任务
 2.检查是否执行</t>
         </is>
       </c>
-      <c r="F6" s="2" t="inlineStr">
+      <c r="F6" t="inlineStr">
         <is>
           <t>当前轮不执行新任务</t>
         </is>
       </c>
-      <c r="G6" s="2" t="inlineStr">
+      <c r="G6" t="inlineStr">
         <is>
           <t>集成测试</t>
         </is>
       </c>
-      <c r="H6" s="2" t="inlineStr">
+      <c r="H6" t="inlineStr">
         <is>
           <t>待执行</t>
         </is>
       </c>
     </row>
     <row r="7">
-      <c r="A7" s="2" t="inlineStr">
+      <c r="A7" t="inlineStr">
         <is>
           <t>TC-SCH-006</t>
         </is>
       </c>
-      <c r="B7" s="2" t="inlineStr">
+      <c r="B7" t="inlineStr">
         <is>
           <t>删除不存在任务</t>
         </is>
       </c>
-      <c r="C7" s="2" t="inlineStr">
+      <c r="C7" t="inlineStr">
         <is>
           <t>P1</t>
         </is>
       </c>
-      <c r="D7" s="2" t="inlineStr">
+      <c r="D7" t="inlineStr">
         <is>
           <t>taskList有2任务</t>
         </is>
       </c>
-      <c r="E7" s="2" t="inlineStr">
+      <c r="E7" t="inlineStr">
         <is>
           <t>1.removeTask(不存在ID)</t>
         </is>
       </c>
-      <c r="F7" s="2" t="inlineStr">
+      <c r="F7" t="inlineStr">
         <is>
           <t>taskList不变或抛指定异常</t>
         </is>
       </c>
-      <c r="G7" s="2" t="inlineStr">
+      <c r="G7" t="inlineStr">
         <is>
           <t>单元测试</t>
         </is>
       </c>
-      <c r="H7" s="2" t="inlineStr">
+      <c r="H7" t="inlineStr">
         <is>
           <t>待执行</t>
         </is>
       </c>
     </row>
     <row r="8">
-      <c r="A8" s="2" t="inlineStr">
+      <c r="A8" t="inlineStr">
         <is>
           <t>TC-SCH-007</t>
         </is>
       </c>
-      <c r="B8" s="2" t="inlineStr">
+      <c r="B8" t="inlineStr">
         <is>
           <t>重复添加去重</t>
         </is>
       </c>
-      <c r="C8" s="2" t="inlineStr">
+      <c r="C8" t="inlineStr">
         <is>
           <t>P1</t>
         </is>
       </c>
-      <c r="D8" s="2" t="inlineStr">
+      <c r="D8" t="inlineStr">
         <is>
           <t>taskList已有OtaTask</t>
         </is>
       </c>
-      <c r="E8" s="2" t="inlineStr">
+      <c r="E8" t="inlineStr">
         <is>
           <t>1.再次addTask(同OtaTask)</t>
         </is>
       </c>
-      <c r="F8" s="2" t="inlineStr">
+      <c r="F8" t="inlineStr">
         <is>
           <t>不可重复添加或自动去重</t>
         </is>
       </c>
-      <c r="G8" s="2" t="inlineStr">
+      <c r="G8" t="inlineStr">
         <is>
           <t>单元测试</t>
         </is>
       </c>
-      <c r="H8" s="2" t="inlineStr">
+      <c r="H8" t="inlineStr">
         <is>
           <t>待执行</t>
         </is>
       </c>
     </row>
     <row r="9">
-      <c r="A9" s="2" t="inlineStr">
+      <c r="A9" t="inlineStr">
         <is>
           <t>TC-SCH-008</t>
         </is>
       </c>
-      <c r="B9" s="2" t="inlineStr">
+      <c r="B9" t="inlineStr">
         <is>
           <t>同优先级FIFO</t>
         </is>
       </c>
-      <c r="C9" s="2" t="inlineStr">
+      <c r="C9" t="inlineStr">
         <is>
           <t>P1</t>
         </is>
       </c>
-      <c r="D9" s="2" t="inlineStr">
+      <c r="D9" t="inlineStr">
         <is>
           <t>3个P1任务</t>
         </is>
       </c>
-      <c r="E9" s="2" t="inlineStr">
+      <c r="E9" t="inlineStr">
         <is>
           <t>1.A-&gt;B-&gt;C顺序添加
 2.执行</t>
         </is>
       </c>
-      <c r="F9" s="2" t="inlineStr">
+      <c r="F9" t="inlineStr">
         <is>
           <t>A-&gt;B-&gt;C顺序执行</t>
         </is>
       </c>
-      <c r="G9" s="2" t="inlineStr">
+      <c r="G9" t="inlineStr">
         <is>
           <t>单元测试</t>
         </is>
       </c>
-      <c r="H9" s="2" t="inlineStr">
+      <c r="H9" t="inlineStr">
         <is>
           <t>待执行</t>
         </is>
       </c>
     </row>
     <row r="10">
-      <c r="A10" s="2" t="inlineStr">
+      <c r="A10" t="inlineStr">
         <is>
           <t>TC-SCH-009</t>
         </is>
       </c>
-      <c r="B10" s="2" t="inlineStr">
+      <c r="B10" t="inlineStr">
         <is>
           <t>任务执行超时</t>
         </is>
       </c>
-      <c r="C10" s="2" t="inlineStr">
+      <c r="C10" t="inlineStr">
         <is>
           <t>P1</t>
         </is>
       </c>
-      <c r="D10" s="2" t="inlineStr">
+      <c r="D10" t="inlineStr">
         <is>
           <t>某任务执行长</t>
         </is>
       </c>
-      <c r="E10" s="2" t="inlineStr">
+      <c r="E10" t="inlineStr">
         <is>
           <t>1.添加长任务
 2.executeTasks加超时</t>
         </is>
       </c>
-      <c r="F10" s="2" t="inlineStr">
+      <c r="F10" t="inlineStr">
         <is>
           <t>超时后标记失败继续下一个</t>
         </is>
       </c>
-      <c r="G10" s="2" t="inlineStr">
+      <c r="G10" t="inlineStr">
         <is>
           <t>集成测试</t>
         </is>
       </c>
-      <c r="H10" s="2" t="inlineStr">
+      <c r="H10" t="inlineStr">
         <is>
           <t>待执行</t>
         </is>
       </c>
     </row>
     <row r="11">
-      <c r="A11" s="2" t="inlineStr">
+      <c r="A11" t="inlineStr">
         <is>
           <t>TC-SCH-010</t>
         </is>
       </c>
-      <c r="B11" s="2" t="inlineStr">
+      <c r="B11" t="inlineStr">
         <is>
           <t>全部完成回调</t>
         </is>
       </c>
-      <c r="C11" s="2" t="inlineStr">
+      <c r="C11" t="inlineStr">
         <is>
           <t>P2</t>
         </is>
       </c>
-      <c r="D11" s="2" t="inlineStr">
+      <c r="D11" t="inlineStr">
         <is>
           <t>3个任务</t>
         </is>
       </c>
-      <c r="E11" s="2" t="inlineStr">
+      <c r="E11" t="inlineStr">
         <is>
           <t>1.注册回调
 2.executeTasks()
 3.验证</t>
         </is>
       </c>
-      <c r="F11" s="2" t="inlineStr">
+      <c r="F11" t="inlineStr">
         <is>
           <t>全部完成后触发回调</t>
         </is>
       </c>
-      <c r="G11" s="2" t="inlineStr">
+      <c r="G11" t="inlineStr">
         <is>
           <t>单元测试</t>
         </is>
       </c>
-      <c r="H11" s="2" t="inlineStr">
+      <c r="H11" t="inlineStr">
         <is>
           <t>待执行</t>
         </is>
       </c>
     </row>
     <row r="12">
-      <c r="A12" s="2" t="inlineStr">
+      <c r="A12" t="inlineStr">
         <is>
           <t>TC-SCH-011</t>
         </is>
       </c>
-      <c r="B12" s="2" t="inlineStr">
+      <c r="B12" t="inlineStr">
         <is>
           <t>并发addTask安全</t>
         </is>
       </c>
-      <c r="C12" s="2" t="inlineStr">
+      <c r="C12" t="inlineStr">
         <is>
           <t>P2</t>
         </is>
       </c>
-      <c r="D12" s="2" t="inlineStr">
+      <c r="D12" t="inlineStr">
         <is>
           <t>多线程</t>
         </is>
       </c>
-      <c r="E12" s="2" t="inlineStr">
+      <c r="E12" t="inlineStr">
         <is>
           <t>1.3线程同时addTask
 2.检查完整性</t>
         </is>
       </c>
-      <c r="F12" s="2" t="inlineStr">
+      <c r="F12" t="inlineStr">
         <is>
           <t>无竞态，所有任务成功添加</t>
         </is>
       </c>
-      <c r="G12" s="2" t="inlineStr">
+      <c r="G12" t="inlineStr">
         <is>
           <t>单元测试</t>
         </is>
       </c>
-      <c r="H12" s="2" t="inlineStr">
+      <c r="H12" t="inlineStr">
         <is>
           <t>待执行</t>
         </is>
@@ -3255,301 +3255,301 @@
   </cols>
   <sheetData>
     <row r="1">
-      <c r="A1" s="1" t="inlineStr">
+      <c r="A1" t="inlineStr">
         <is>
           <t>用例ID</t>
         </is>
       </c>
-      <c r="B1" s="1" t="inlineStr">
+      <c r="B1" t="inlineStr">
         <is>
           <t>用例名称</t>
         </is>
       </c>
-      <c r="C1" s="1" t="inlineStr">
+      <c r="C1" t="inlineStr">
         <is>
           <t>优先级</t>
         </is>
       </c>
-      <c r="D1" s="1" t="inlineStr">
+      <c r="D1" t="inlineStr">
         <is>
           <t>前置条件</t>
         </is>
       </c>
-      <c r="E1" s="1" t="inlineStr">
+      <c r="E1" t="inlineStr">
         <is>
           <t>测试步骤</t>
         </is>
       </c>
-      <c r="F1" s="1" t="inlineStr">
+      <c r="F1" t="inlineStr">
         <is>
           <t>预期结果</t>
         </is>
       </c>
-      <c r="G1" s="1" t="inlineStr">
+      <c r="G1" t="inlineStr">
         <is>
           <t>测试类型</t>
         </is>
       </c>
-      <c r="H1" s="1" t="inlineStr">
+      <c r="H1" t="inlineStr">
         <is>
           <t>状态</t>
         </is>
       </c>
     </row>
     <row r="2">
-      <c r="A2" s="2" t="inlineStr">
+      <c r="A2" t="inlineStr">
         <is>
           <t>TC-APP-001</t>
         </is>
       </c>
-      <c r="B2" s="2" t="inlineStr">
+      <c r="B2" t="inlineStr">
         <is>
           <t>应用正常启动</t>
         </is>
       </c>
-      <c r="C2" s="2" t="inlineStr">
+      <c r="C2" t="inlineStr">
         <is>
           <t>P0</t>
         </is>
       </c>
-      <c r="D2" s="2" t="inlineStr">
+      <c r="D2" t="inlineStr">
         <is>
           <t>MM_APP已创建</t>
         </is>
       </c>
-      <c r="E2" s="2" t="inlineStr">
+      <c r="E2" t="inlineStr">
         <is>
           <t>1.start()
 2.检查调度器初始化
 3.检查任务注册</t>
         </is>
       </c>
-      <c r="F2" s="2" t="inlineStr">
+      <c r="F2" t="inlineStr">
         <is>
           <t>调度器初始化，任务注册完毕</t>
         </is>
       </c>
-      <c r="G2" s="2" t="inlineStr">
+      <c r="G2" t="inlineStr">
         <is>
           <t>集成测试</t>
         </is>
       </c>
-      <c r="H2" s="2" t="inlineStr">
+      <c r="H2" t="inlineStr">
         <is>
           <t>待执行</t>
         </is>
       </c>
     </row>
     <row r="3">
-      <c r="A3" s="2" t="inlineStr">
+      <c r="A3" t="inlineStr">
         <is>
           <t>TC-APP-002</t>
         </is>
       </c>
-      <c r="B3" s="2" t="inlineStr">
+      <c r="B3" t="inlineStr">
         <is>
           <t>应用正常停止</t>
         </is>
       </c>
-      <c r="C3" s="2" t="inlineStr">
+      <c r="C3" t="inlineStr">
         <is>
           <t>P0</t>
         </is>
       </c>
-      <c r="D3" s="2" t="inlineStr">
+      <c r="D3" t="inlineStr">
         <is>
           <t>MM_APP运行中</t>
         </is>
       </c>
-      <c r="E3" s="2" t="inlineStr">
+      <c r="E3" t="inlineStr">
         <is>
           <t>1.stop()
 2.检查任务停止
 3.检查资源释放</t>
         </is>
       </c>
-      <c r="F3" s="2" t="inlineStr">
+      <c r="F3" t="inlineStr">
         <is>
           <t>所有任务停止，资源释放</t>
         </is>
       </c>
-      <c r="G3" s="2" t="inlineStr">
+      <c r="G3" t="inlineStr">
         <is>
           <t>集成测试</t>
         </is>
       </c>
-      <c r="H3" s="2" t="inlineStr">
+      <c r="H3" t="inlineStr">
         <is>
           <t>待执行</t>
         </is>
       </c>
     </row>
     <row r="4">
-      <c r="A4" s="2" t="inlineStr">
+      <c r="A4" t="inlineStr">
         <is>
           <t>TC-APP-003</t>
         </is>
       </c>
-      <c r="B4" s="2" t="inlineStr">
+      <c r="B4" t="inlineStr">
         <is>
           <t>获取应用信息</t>
         </is>
       </c>
-      <c r="C4" s="2" t="inlineStr">
+      <c r="C4" t="inlineStr">
         <is>
           <t>P0</t>
         </is>
       </c>
-      <c r="D4" s="2" t="inlineStr">
+      <c r="D4" t="inlineStr">
         <is>
           <t>MM_APP已启动</t>
         </is>
       </c>
-      <c r="E4" s="2" t="inlineStr">
+      <c r="E4" t="inlineStr">
         <is>
           <t>1.检查appName
 2.检查version</t>
         </is>
       </c>
-      <c r="F4" s="2" t="inlineStr">
+      <c r="F4" t="inlineStr">
         <is>
           <t>appName/version非空，格式正确</t>
         </is>
       </c>
-      <c r="G4" s="2" t="inlineStr">
+      <c r="G4" t="inlineStr">
         <is>
           <t>单元测试</t>
         </is>
       </c>
-      <c r="H4" s="2" t="inlineStr">
+      <c r="H4" t="inlineStr">
         <is>
           <t>待执行</t>
         </is>
       </c>
     </row>
     <row r="5">
-      <c r="A5" s="2" t="inlineStr">
+      <c r="A5" t="inlineStr">
         <is>
           <t>TC-APP-004</t>
         </is>
       </c>
-      <c r="B5" s="2" t="inlineStr">
+      <c r="B5" t="inlineStr">
         <is>
           <t>重复启动防护</t>
         </is>
       </c>
-      <c r="C5" s="2" t="inlineStr">
+      <c r="C5" t="inlineStr">
         <is>
           <t>P1</t>
         </is>
       </c>
-      <c r="D5" s="2" t="inlineStr">
+      <c r="D5" t="inlineStr">
         <is>
           <t>MM_APP已启动</t>
         </is>
       </c>
-      <c r="E5" s="2" t="inlineStr">
+      <c r="E5" t="inlineStr">
         <is>
           <t>1.再次start()</t>
         </is>
       </c>
-      <c r="F5" s="2" t="inlineStr">
+      <c r="F5" t="inlineStr">
         <is>
           <t>不重复初始化</t>
         </is>
       </c>
-      <c r="G5" s="2" t="inlineStr">
+      <c r="G5" t="inlineStr">
         <is>
           <t>单元测试</t>
         </is>
       </c>
-      <c r="H5" s="2" t="inlineStr">
+      <c r="H5" t="inlineStr">
         <is>
           <t>待执行</t>
         </is>
       </c>
     </row>
     <row r="6">
-      <c r="A6" s="2" t="inlineStr">
+      <c r="A6" t="inlineStr">
         <is>
           <t>TC-APP-005</t>
         </is>
       </c>
-      <c r="B6" s="2" t="inlineStr">
+      <c r="B6" t="inlineStr">
         <is>
           <t>未启动就停止</t>
         </is>
       </c>
-      <c r="C6" s="2" t="inlineStr">
+      <c r="C6" t="inlineStr">
         <is>
           <t>P1</t>
         </is>
       </c>
-      <c r="D6" s="2" t="inlineStr">
+      <c r="D6" t="inlineStr">
         <is>
           <t>MM_APP未启动</t>
         </is>
       </c>
-      <c r="E6" s="2" t="inlineStr">
+      <c r="E6" t="inlineStr">
         <is>
           <t>1.直接stop()</t>
         </is>
       </c>
-      <c r="F6" s="2" t="inlineStr">
+      <c r="F6" t="inlineStr">
         <is>
           <t>不抛异常</t>
         </is>
       </c>
-      <c r="G6" s="2" t="inlineStr">
+      <c r="G6" t="inlineStr">
         <is>
           <t>单元测试</t>
         </is>
       </c>
-      <c r="H6" s="2" t="inlineStr">
+      <c r="H6" t="inlineStr">
         <is>
           <t>待执行</t>
         </is>
       </c>
     </row>
     <row r="7">
-      <c r="A7" s="2" t="inlineStr">
+      <c r="A7" t="inlineStr">
         <is>
           <t>TC-APP-006</t>
         </is>
       </c>
-      <c r="B7" s="2" t="inlineStr">
+      <c r="B7" t="inlineStr">
         <is>
           <t>启动失败回滚</t>
         </is>
       </c>
-      <c r="C7" s="2" t="inlineStr">
+      <c r="C7" t="inlineStr">
         <is>
           <t>P2</t>
         </is>
       </c>
-      <c r="D7" s="2" t="inlineStr">
+      <c r="D7" t="inlineStr">
         <is>
           <t>依赖不可用</t>
         </is>
       </c>
-      <c r="E7" s="2" t="inlineStr">
+      <c r="E7" t="inlineStr">
         <is>
           <t>1.模拟初始化失败
 2.start()
 3.检查状态</t>
         </is>
       </c>
-      <c r="F7" s="2" t="inlineStr">
+      <c r="F7" t="inlineStr">
         <is>
           <t>启动失败时状态仍为stopped</t>
         </is>
       </c>
-      <c r="G7" s="2" t="inlineStr">
+      <c r="G7" t="inlineStr">
         <is>
           <t>单元测试</t>
         </is>
       </c>
-      <c r="H7" s="2" t="inlineStr">
+      <c r="H7" t="inlineStr">
         <is>
           <t>待执行</t>
         </is>
@@ -3580,69 +3580,69 @@
   </cols>
   <sheetData>
     <row r="1">
-      <c r="A1" s="1" t="inlineStr">
+      <c r="A1" t="inlineStr">
         <is>
           <t>用例ID</t>
         </is>
       </c>
-      <c r="B1" s="1" t="inlineStr">
+      <c r="B1" t="inlineStr">
         <is>
           <t>用例名称</t>
         </is>
       </c>
-      <c r="C1" s="1" t="inlineStr">
+      <c r="C1" t="inlineStr">
         <is>
           <t>优先级</t>
         </is>
       </c>
-      <c r="D1" s="1" t="inlineStr">
+      <c r="D1" t="inlineStr">
         <is>
           <t>前置条件</t>
         </is>
       </c>
-      <c r="E1" s="1" t="inlineStr">
+      <c r="E1" t="inlineStr">
         <is>
           <t>测试步骤</t>
         </is>
       </c>
-      <c r="F1" s="1" t="inlineStr">
+      <c r="F1" t="inlineStr">
         <is>
           <t>预期结果</t>
         </is>
       </c>
-      <c r="G1" s="1" t="inlineStr">
+      <c r="G1" t="inlineStr">
         <is>
           <t>测试类型</t>
         </is>
       </c>
-      <c r="H1" s="1" t="inlineStr">
+      <c r="H1" t="inlineStr">
         <is>
           <t>状态</t>
         </is>
       </c>
     </row>
     <row r="2">
-      <c r="A2" s="2" t="inlineStr">
+      <c r="A2" t="inlineStr">
         <is>
           <t>TC-INT-001</t>
         </is>
       </c>
-      <c r="B2" s="2" t="inlineStr">
+      <c r="B2" t="inlineStr">
         <is>
           <t>完整启动-调度-停止流程</t>
         </is>
       </c>
-      <c r="C2" s="2" t="inlineStr">
+      <c r="C2" t="inlineStr">
         <is>
           <t>P0</t>
         </is>
       </c>
-      <c r="D2" s="2" t="inlineStr">
+      <c r="D2" t="inlineStr">
         <is>
           <t>系统初始</t>
         </is>
       </c>
-      <c r="E2" s="2" t="inlineStr">
+      <c r="E2" t="inlineStr">
         <is>
           <t>1.start()
 2.添加OtaTask+CrowTask
@@ -3650,497 +3650,497 @@
 4.stop()</t>
         </is>
       </c>
-      <c r="F2" s="2" t="inlineStr">
+      <c r="F2" t="inlineStr">
         <is>
           <t>全流程无异常</t>
         </is>
       </c>
-      <c r="G2" s="2" t="inlineStr">
+      <c r="G2" t="inlineStr">
         <is>
           <t>端到端</t>
         </is>
       </c>
-      <c r="H2" s="2" t="inlineStr">
+      <c r="H2" t="inlineStr">
         <is>
           <t>待执行</t>
         </is>
       </c>
     </row>
     <row r="3">
-      <c r="A3" s="2" t="inlineStr">
+      <c r="A3" t="inlineStr">
         <is>
           <t>TC-INT-002</t>
         </is>
       </c>
-      <c r="B3" s="2" t="inlineStr">
+      <c r="B3" t="inlineStr">
         <is>
           <t>CrowTask打断SentinelTask</t>
         </is>
       </c>
-      <c r="C3" s="2" t="inlineStr">
+      <c r="C3" t="inlineStr">
         <is>
           <t>P0</t>
         </is>
       </c>
-      <c r="D3" s="2" t="inlineStr">
+      <c r="D3" t="inlineStr">
         <is>
           <t>哨兵运行+鸡叫预约</t>
         </is>
       </c>
-      <c r="E3" s="2" t="inlineStr">
+      <c r="E3" t="inlineStr">
         <is>
           <t>1.哨兵运行
 2.鸡叫到达
 3.被打断-&gt;鸡叫-&gt;恢复</t>
         </is>
       </c>
-      <c r="F3" s="2" t="inlineStr">
+      <c r="F3" t="inlineStr">
         <is>
           <t>打断链: 暂停-&gt;鸡叫-&gt;恢复</t>
         </is>
       </c>
-      <c r="G3" s="2" t="inlineStr">
+      <c r="G3" t="inlineStr">
         <is>
           <t>端到端</t>
         </is>
       </c>
-      <c r="H3" s="2" t="inlineStr">
+      <c r="H3" t="inlineStr">
         <is>
           <t>待执行</t>
         </is>
       </c>
     </row>
     <row r="4">
-      <c r="A4" s="2" t="inlineStr">
+      <c r="A4" t="inlineStr">
         <is>
           <t>TC-INT-003</t>
         </is>
       </c>
-      <c r="B4" s="2" t="inlineStr">
+      <c r="B4" t="inlineStr">
         <is>
           <t>Ota升级清除鸡叫</t>
         </is>
       </c>
-      <c r="C4" s="2" t="inlineStr">
+      <c r="C4" t="inlineStr">
         <is>
           <t>P0</t>
         </is>
       </c>
-      <c r="D4" s="2" t="inlineStr">
+      <c r="D4" t="inlineStr">
         <is>
           <t>鸡叫有累计</t>
         </is>
       </c>
-      <c r="E4" s="2" t="inlineStr">
+      <c r="E4" t="inlineStr">
         <is>
           <t>1.触发OtaTask
 2.检查累计清零
 3.检查预约清除</t>
         </is>
       </c>
-      <c r="F4" s="2" t="inlineStr">
+      <c r="F4" t="inlineStr">
         <is>
           <t>升级后鸡叫相关清零</t>
         </is>
       </c>
-      <c r="G4" s="2" t="inlineStr">
+      <c r="G4" t="inlineStr">
         <is>
           <t>端到端</t>
         </is>
       </c>
-      <c r="H4" s="2" t="inlineStr">
+      <c r="H4" t="inlineStr">
         <is>
           <t>待执行</t>
         </is>
       </c>
     </row>
     <row r="5">
-      <c r="A5" s="2" t="inlineStr">
+      <c r="A5" t="inlineStr">
         <is>
           <t>TC-INT-004</t>
         </is>
       </c>
-      <c r="B5" s="2" t="inlineStr">
+      <c r="B5" t="inlineStr">
         <is>
           <t>鸡叫中升级到达</t>
         </is>
       </c>
-      <c r="C5" s="2" t="inlineStr">
+      <c r="C5" t="inlineStr">
         <is>
           <t>P0</t>
         </is>
       </c>
-      <c r="D5" s="2" t="inlineStr">
+      <c r="D5" t="inlineStr">
         <is>
           <t>CrowTask鸡叫中</t>
         </is>
       </c>
-      <c r="E5" s="2" t="inlineStr">
+      <c r="E5" t="inlineStr">
         <is>
           <t>1.鸡叫中
 2.OtaTask升级触发
 3.检查</t>
         </is>
       </c>
-      <c r="F5" s="2" t="inlineStr">
+      <c r="F5" t="inlineStr">
         <is>
           <t>鸡叫不可打断，升级等待</t>
         </is>
       </c>
-      <c r="G5" s="2" t="inlineStr">
+      <c r="G5" t="inlineStr">
         <is>
           <t>端到端</t>
         </is>
       </c>
-      <c r="H5" s="2" t="inlineStr">
+      <c r="H5" t="inlineStr">
         <is>
           <t>待执行</t>
         </is>
       </c>
     </row>
     <row r="6">
-      <c r="A6" s="2" t="inlineStr">
+      <c r="A6" t="inlineStr">
         <is>
           <t>TC-INT-005</t>
         </is>
       </c>
-      <c r="B6" s="2" t="inlineStr">
+      <c r="B6" t="inlineStr">
         <is>
           <t>多任务并发调度</t>
         </is>
       </c>
-      <c r="C6" s="2" t="inlineStr">
+      <c r="C6" t="inlineStr">
         <is>
           <t>P0</t>
         </is>
       </c>
-      <c r="D6" s="2" t="inlineStr">
+      <c r="D6" t="inlineStr">
         <is>
           <t>5个不同优先级任务</t>
         </is>
       </c>
-      <c r="E6" s="2" t="inlineStr">
+      <c r="E6" t="inlineStr">
         <is>
           <t>1.同时到达执行时间
 2.调度
 3.检查顺序</t>
         </is>
       </c>
-      <c r="F6" s="2" t="inlineStr">
+      <c r="F6" t="inlineStr">
         <is>
           <t>全部按优先级+到达顺序执行</t>
         </is>
       </c>
-      <c r="G6" s="2" t="inlineStr">
+      <c r="G6" t="inlineStr">
         <is>
           <t>端到端</t>
         </is>
       </c>
-      <c r="H6" s="2" t="inlineStr">
+      <c r="H6" t="inlineStr">
         <is>
           <t>待执行</t>
         </is>
       </c>
     </row>
     <row r="7">
-      <c r="A7" s="2" t="inlineStr">
+      <c r="A7" t="inlineStr">
         <is>
           <t>TC-INT-006</t>
         </is>
       </c>
-      <c r="B7" s="2" t="inlineStr">
+      <c r="B7" t="inlineStr">
         <is>
           <t>7天稳定性测试</t>
         </is>
       </c>
-      <c r="C7" s="2" t="inlineStr">
+      <c r="C7" t="inlineStr">
         <is>
           <t>P0</t>
         </is>
       </c>
-      <c r="D7" s="2" t="inlineStr">
+      <c r="D7" t="inlineStr">
         <is>
           <t>系统正常运行</t>
         </is>
       </c>
-      <c r="E7" s="2" t="inlineStr">
+      <c r="E7" t="inlineStr">
         <is>
           <t>1.模拟运行7天
 2.每日鸡叫+随机升级
 3.检查内存</t>
         </is>
       </c>
-      <c r="F7" s="2" t="inlineStr">
+      <c r="F7" t="inlineStr">
         <is>
           <t>无内存泄漏，无任务累积</t>
         </is>
       </c>
-      <c r="G7" s="2" t="inlineStr">
+      <c r="G7" t="inlineStr">
         <is>
           <t>性能测试</t>
         </is>
       </c>
-      <c r="H7" s="2" t="inlineStr">
+      <c r="H7" t="inlineStr">
         <is>
           <t>待执行</t>
         </is>
       </c>
     </row>
     <row r="8">
-      <c r="A8" s="2" t="inlineStr">
+      <c r="A8" t="inlineStr">
         <is>
           <t>TC-INT-007</t>
         </is>
       </c>
-      <c r="B8" s="2" t="inlineStr">
+      <c r="B8" t="inlineStr">
         <is>
           <t>鸡叫累计循环</t>
         </is>
       </c>
-      <c r="C8" s="2" t="inlineStr">
+      <c r="C8" t="inlineStr">
         <is>
           <t>P1</t>
         </is>
       </c>
-      <c r="D8" s="2" t="inlineStr">
+      <c r="D8" t="inlineStr">
         <is>
           <t>正常运行</t>
         </is>
       </c>
-      <c r="E8" s="2" t="inlineStr">
+      <c r="E8" t="inlineStr">
         <is>
           <t>1.3次鸡叫-&gt;升级清除-&gt;2次鸡叫
 2.验证</t>
         </is>
       </c>
-      <c r="F8" s="2" t="inlineStr">
+      <c r="F8" t="inlineStr">
         <is>
           <t>清除-&gt;再累计循环正确</t>
         </is>
       </c>
-      <c r="G8" s="2" t="inlineStr">
+      <c r="G8" t="inlineStr">
         <is>
           <t>端到端</t>
         </is>
       </c>
-      <c r="H8" s="2" t="inlineStr">
+      <c r="H8" t="inlineStr">
         <is>
           <t>待执行</t>
         </is>
       </c>
     </row>
     <row r="9">
-      <c r="A9" s="2" t="inlineStr">
+      <c r="A9" t="inlineStr">
         <is>
           <t>TC-INT-008</t>
         </is>
       </c>
-      <c r="B9" s="2" t="inlineStr">
+      <c r="B9" t="inlineStr">
         <is>
           <t>三任务优先级仲裁</t>
         </is>
       </c>
-      <c r="C9" s="2" t="inlineStr">
+      <c r="C9" t="inlineStr">
         <is>
           <t>P1</t>
         </is>
       </c>
-      <c r="D9" s="2" t="inlineStr">
+      <c r="D9" t="inlineStr">
         <is>
           <t>哨兵/鸡叫/升级同时</t>
         </is>
       </c>
-      <c r="E9" s="2" t="inlineStr">
+      <c r="E9" t="inlineStr">
         <is>
           <t>1.哨兵执行中
 2.鸡叫+升级同时到达</t>
         </is>
       </c>
-      <c r="F9" s="2" t="inlineStr">
+      <c r="F9" t="inlineStr">
         <is>
           <t>鸡叫(P0打断)-&gt;升级(P1)-&gt;哨兵恢复</t>
         </is>
       </c>
-      <c r="G9" s="2" t="inlineStr">
+      <c r="G9" t="inlineStr">
         <is>
           <t>端到端</t>
         </is>
       </c>
-      <c r="H9" s="2" t="inlineStr">
+      <c r="H9" t="inlineStr">
         <is>
           <t>待执行</t>
         </is>
       </c>
     </row>
     <row r="10">
-      <c r="A10" s="2" t="inlineStr">
+      <c r="A10" t="inlineStr">
         <is>
           <t>TC-INT-009</t>
         </is>
       </c>
-      <c r="B10" s="2" t="inlineStr">
+      <c r="B10" t="inlineStr">
         <is>
           <t>异常任务后恢复</t>
         </is>
       </c>
-      <c r="C10" s="2" t="inlineStr">
+      <c r="C10" t="inlineStr">
         <is>
           <t>P1</t>
         </is>
       </c>
-      <c r="D10" s="2" t="inlineStr">
+      <c r="D10" t="inlineStr">
         <is>
           <t>某任务会异常</t>
         </is>
       </c>
-      <c r="E10" s="2" t="inlineStr">
+      <c r="E10" t="inlineStr">
         <is>
           <t>1.添加异常任务
 2.executeTasks()
 3.检查后续</t>
         </is>
       </c>
-      <c r="F10" s="2" t="inlineStr">
+      <c r="F10" t="inlineStr">
         <is>
           <t>异常任务失败后续正常执行</t>
         </is>
       </c>
-      <c r="G10" s="2" t="inlineStr">
+      <c r="G10" t="inlineStr">
         <is>
           <t>端到端</t>
         </is>
       </c>
-      <c r="H10" s="2" t="inlineStr">
+      <c r="H10" t="inlineStr">
         <is>
           <t>待执行</t>
         </is>
       </c>
     </row>
     <row r="11">
-      <c r="A11" s="2" t="inlineStr">
+      <c r="A11" t="inlineStr">
         <is>
           <t>TC-INT-010</t>
         </is>
       </c>
-      <c r="B11" s="2" t="inlineStr">
+      <c r="B11" t="inlineStr">
         <is>
           <t>启停压力测试</t>
         </is>
       </c>
-      <c r="C11" s="2" t="inlineStr">
+      <c r="C11" t="inlineStr">
         <is>
           <t>P1</t>
         </is>
       </c>
-      <c r="D11" s="2" t="inlineStr">
+      <c r="D11" t="inlineStr">
         <is>
           <t>系统初始</t>
         </is>
       </c>
-      <c r="E11" s="2" t="inlineStr">
+      <c r="E11" t="inlineStr">
         <is>
           <t>1.start/stop重复100次
 2.检查资源</t>
         </is>
       </c>
-      <c r="F11" s="2" t="inlineStr">
+      <c r="F11" t="inlineStr">
         <is>
           <t>无泄漏</t>
         </is>
       </c>
-      <c r="G11" s="2" t="inlineStr">
+      <c r="G11" t="inlineStr">
         <is>
           <t>性能测试</t>
         </is>
       </c>
-      <c r="H11" s="2" t="inlineStr">
+      <c r="H11" t="inlineStr">
         <is>
           <t>待执行</t>
         </is>
       </c>
     </row>
     <row r="12">
-      <c r="A12" s="2" t="inlineStr">
+      <c r="A12" t="inlineStr">
         <is>
           <t>TC-INT-011</t>
         </is>
       </c>
-      <c r="B12" s="2" t="inlineStr">
+      <c r="B12" t="inlineStr">
         <is>
           <t>时间跳变处理</t>
         </is>
       </c>
-      <c r="C12" s="2" t="inlineStr">
+      <c r="C12" t="inlineStr">
         <is>
           <t>P2</t>
         </is>
       </c>
-      <c r="D12" s="2" t="inlineStr">
+      <c r="D12" t="inlineStr">
         <is>
           <t>运行中</t>
         </is>
       </c>
-      <c r="E12" s="2" t="inlineStr">
+      <c r="E12" t="inlineStr">
         <is>
           <t>1.时间向前跳24h
 2.检查调度</t>
         </is>
       </c>
-      <c r="F12" s="2" t="inlineStr">
+      <c r="F12" t="inlineStr">
         <is>
           <t>调度自动纠正</t>
         </is>
       </c>
-      <c r="G12" s="2" t="inlineStr">
+      <c r="G12" t="inlineStr">
         <is>
           <t>端到端</t>
         </is>
       </c>
-      <c r="H12" s="2" t="inlineStr">
+      <c r="H12" t="inlineStr">
         <is>
           <t>待执行</t>
         </is>
       </c>
     </row>
     <row r="13">
-      <c r="A13" s="2" t="inlineStr">
+      <c r="A13" t="inlineStr">
         <is>
           <t>TC-INT-012</t>
         </is>
       </c>
-      <c r="B13" s="2" t="inlineStr">
+      <c r="B13" t="inlineStr">
         <is>
           <t>断电恢复</t>
         </is>
       </c>
-      <c r="C13" s="2" t="inlineStr">
+      <c r="C13" t="inlineStr">
         <is>
           <t>P2</t>
         </is>
       </c>
-      <c r="D13" s="2" t="inlineStr">
+      <c r="D13" t="inlineStr">
         <is>
           <t>运行中</t>
         </is>
       </c>
-      <c r="E13" s="2" t="inlineStr">
+      <c r="E13" t="inlineStr">
         <is>
           <t>1.任务执行中
 2.模拟断电
 3.重启检查</t>
         </is>
       </c>
-      <c r="F13" s="2" t="inlineStr">
+      <c r="F13" t="inlineStr">
         <is>
           <t>重启后未完成恢复或标记失败</t>
         </is>
       </c>
-      <c r="G13" s="2" t="inlineStr">
+      <c r="G13" t="inlineStr">
         <is>
           <t>端到端</t>
         </is>
       </c>
-      <c r="H13" s="2" t="inlineStr">
+      <c r="H13" t="inlineStr">
         <is>
           <t>待执行</t>
         </is>
@@ -4169,256 +4169,256 @@
   </cols>
   <sheetData>
     <row r="1">
-      <c r="A1" s="1" t="inlineStr">
+      <c r="A1" t="inlineStr">
         <is>
           <t>用例ID</t>
         </is>
       </c>
-      <c r="B1" s="1" t="inlineStr">
+      <c r="B1" t="inlineStr">
         <is>
           <t>源类</t>
         </is>
       </c>
-      <c r="C1" s="1" t="inlineStr">
+      <c r="C1" t="inlineStr">
         <is>
           <t>目标类</t>
         </is>
       </c>
-      <c r="D1" s="1" t="inlineStr">
+      <c r="D1" t="inlineStr">
         <is>
           <t>关系类型</t>
         </is>
       </c>
-      <c r="E1" s="1" t="inlineStr">
+      <c r="E1" t="inlineStr">
         <is>
           <t>验证方法</t>
         </is>
       </c>
-      <c r="F1" s="1" t="inlineStr">
+      <c r="F1" t="inlineStr">
         <is>
           <t>状态</t>
         </is>
       </c>
     </row>
     <row r="2">
-      <c r="A2" s="2" t="inlineStr">
+      <c r="A2" t="inlineStr">
         <is>
           <t>TC-REL-001</t>
         </is>
       </c>
-      <c r="B2" s="2" t="inlineStr">
+      <c r="B2" t="inlineStr">
         <is>
           <t>OtaTask</t>
         </is>
       </c>
-      <c r="C2" s="2" t="inlineStr">
+      <c r="C2" t="inlineStr">
         <is>
           <t>BaseTask</t>
         </is>
       </c>
-      <c r="D2" s="2" t="inlineStr">
+      <c r="D2" t="inlineStr">
         <is>
           <t>inheritance</t>
         </is>
       </c>
-      <c r="E2" s="2" t="inlineStr">
+      <c r="E2" t="inlineStr">
         <is>
           <t>OtaTask instanceof BaseTask; 继承taskId/priority/execute()</t>
         </is>
       </c>
-      <c r="F2" s="2" t="inlineStr">
+      <c r="F2" t="inlineStr">
         <is>
           <t>待验证</t>
         </is>
       </c>
     </row>
     <row r="3">
-      <c r="A3" s="2" t="inlineStr">
+      <c r="A3" t="inlineStr">
         <is>
           <t>TC-REL-002</t>
         </is>
       </c>
-      <c r="B3" s="2" t="inlineStr">
+      <c r="B3" t="inlineStr">
         <is>
           <t>CrowTask</t>
         </is>
       </c>
-      <c r="C3" s="2" t="inlineStr">
+      <c r="C3" t="inlineStr">
         <is>
           <t>BaseTask</t>
         </is>
       </c>
-      <c r="D3" s="2" t="inlineStr">
+      <c r="D3" t="inlineStr">
         <is>
           <t>inheritance</t>
         </is>
       </c>
-      <c r="E3" s="2" t="inlineStr">
+      <c r="E3" t="inlineStr">
         <is>
           <t>CrowTask instanceof BaseTask; 可调用getTaskId()</t>
         </is>
       </c>
-      <c r="F3" s="2" t="inlineStr">
+      <c r="F3" t="inlineStr">
         <is>
           <t>待验证</t>
         </is>
       </c>
     </row>
     <row r="4">
-      <c r="A4" s="2" t="inlineStr">
+      <c r="A4" t="inlineStr">
         <is>
           <t>TC-REL-003</t>
         </is>
       </c>
-      <c r="B4" s="2" t="inlineStr">
+      <c r="B4" t="inlineStr">
         <is>
           <t>SentinelTask</t>
         </is>
       </c>
-      <c r="C4" s="2" t="inlineStr">
+      <c r="C4" t="inlineStr">
         <is>
           <t>BaseTask</t>
         </is>
       </c>
-      <c r="D4" s="2" t="inlineStr">
+      <c r="D4" t="inlineStr">
         <is>
           <t>inheritance</t>
         </is>
       </c>
-      <c r="E4" s="2" t="inlineStr">
+      <c r="E4" t="inlineStr">
         <is>
           <t>SentinelTask instanceof BaseTask; 可执行interrupt/resume</t>
         </is>
       </c>
-      <c r="F4" s="2" t="inlineStr">
+      <c r="F4" t="inlineStr">
         <is>
           <t>待验证</t>
         </is>
       </c>
     </row>
     <row r="5">
-      <c r="A5" s="2" t="inlineStr">
+      <c r="A5" t="inlineStr">
         <is>
           <t>TC-REL-004</t>
         </is>
       </c>
-      <c r="B5" s="2" t="inlineStr">
+      <c r="B5" t="inlineStr">
         <is>
           <t>CrowTask</t>
         </is>
       </c>
-      <c r="C5" s="2" t="inlineStr">
+      <c r="C5" t="inlineStr">
         <is>
           <t>TaskScheduler</t>
         </is>
       </c>
-      <c r="D5" s="2" t="inlineStr">
+      <c r="D5" t="inlineStr">
         <is>
           <t>aggregation</t>
         </is>
       </c>
-      <c r="E5" s="2" t="inlineStr">
+      <c r="E5" t="inlineStr">
         <is>
           <t>TaskScheduler删除后CrowTask仍可独立存在</t>
         </is>
       </c>
-      <c r="F5" s="2" t="inlineStr">
+      <c r="F5" t="inlineStr">
         <is>
           <t>待验证</t>
         </is>
       </c>
     </row>
     <row r="6">
-      <c r="A6" s="2" t="inlineStr">
+      <c r="A6" t="inlineStr">
         <is>
           <t>TC-REL-005</t>
         </is>
       </c>
-      <c r="B6" s="2" t="inlineStr">
+      <c r="B6" t="inlineStr">
         <is>
           <t>TaskScheduler</t>
         </is>
       </c>
-      <c r="C6" s="2" t="inlineStr">
+      <c r="C6" t="inlineStr">
         <is>
           <t>MM_APP</t>
         </is>
       </c>
-      <c r="D6" s="2" t="inlineStr">
+      <c r="D6" t="inlineStr">
         <is>
           <t>aggregation</t>
         </is>
       </c>
-      <c r="E6" s="2" t="inlineStr">
+      <c r="E6" t="inlineStr">
         <is>
           <t>MM_APP停止不影响调度器taskList数据</t>
         </is>
       </c>
-      <c r="F6" s="2" t="inlineStr">
+      <c r="F6" t="inlineStr">
         <is>
           <t>待验证</t>
         </is>
       </c>
     </row>
     <row r="7">
-      <c r="A7" s="2" t="inlineStr">
+      <c r="A7" t="inlineStr">
         <is>
           <t>TC-REL-006</t>
         </is>
       </c>
-      <c r="B7" s="2" t="inlineStr">
+      <c r="B7" t="inlineStr">
         <is>
           <t>OtaTask</t>
         </is>
       </c>
-      <c r="C7" s="2" t="inlineStr">
+      <c r="C7" t="inlineStr">
         <is>
           <t>TaskScheduler</t>
         </is>
       </c>
-      <c r="D7" s="2" t="inlineStr">
+      <c r="D7" t="inlineStr">
         <is>
           <t>association</t>
         </is>
       </c>
-      <c r="E7" s="2" t="inlineStr">
+      <c r="E7" t="inlineStr">
         <is>
           <t>OtaTask注册到调度器后可被调度执行</t>
         </is>
       </c>
-      <c r="F7" s="2" t="inlineStr">
+      <c r="F7" t="inlineStr">
         <is>
           <t>待验证</t>
         </is>
       </c>
     </row>
     <row r="8">
-      <c r="A8" s="2" t="inlineStr">
+      <c r="A8" t="inlineStr">
         <is>
           <t>TC-REL-007</t>
         </is>
       </c>
-      <c r="B8" s="2" t="inlineStr">
+      <c r="B8" t="inlineStr">
         <is>
           <t>SentinelTask</t>
         </is>
       </c>
-      <c r="C8" s="2" t="inlineStr">
+      <c r="C8" t="inlineStr">
         <is>
           <t>TaskScheduler</t>
         </is>
       </c>
-      <c r="D8" s="2" t="inlineStr">
+      <c r="D8" t="inlineStr">
         <is>
           <t>association</t>
         </is>
       </c>
-      <c r="E8" s="2" t="inlineStr">
+      <c r="E8" t="inlineStr">
         <is>
           <t>哨兵通过调度器与其他任务协调</t>
         </is>
       </c>
-      <c r="F8" s="2" t="inlineStr">
+      <c r="F8" t="inlineStr">
         <is>
           <t>待验证</t>
         </is>
